--- a/results/block2_results/stenosis/Synthetic_2/total_df_Synthetic_2.xlsx
+++ b/results/block2_results/stenosis/Synthetic_2/total_df_Synthetic_2.xlsx
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>50.00626754760742</v>
+        <v>50.00571823120117</v>
       </c>
       <c r="D2" t="n">
-        <v>50.00995635986328</v>
+        <v>50.01014709472656</v>
       </c>
       <c r="E2" t="n">
-        <v>50.00577163696289</v>
+        <v>50.09407806396484</v>
       </c>
       <c r="F2" t="n">
-        <v>5.077139341010465</v>
+        <v>5.077283098638796</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -558,28 +558,28 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L2" t="n">
-        <v>78.5399454490972</v>
+        <v>82.5503367289798</v>
       </c>
       <c r="M2" t="n">
-        <v>22.98966487340354</v>
+        <v>23.07797321490169</v>
       </c>
       <c r="N2" t="n">
-        <v>314.1315652890347</v>
+        <v>313.3667832967068</v>
       </c>
       <c r="O2" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="P2" t="n">
-        <v>314.145415324007</v>
+        <v>313.5528141633909</v>
       </c>
       <c r="Q2" t="b">
         <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>74.99885670204935</v>
+        <v>73.67258943306337</v>
       </c>
     </row>
     <row r="3">
@@ -592,16 +592,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>50.00571823120117</v>
+        <v>50.00626754760742</v>
       </c>
       <c r="D3" t="n">
-        <v>50.01014709472656</v>
+        <v>50.00995635986328</v>
       </c>
       <c r="E3" t="n">
-        <v>50.09407806396484</v>
+        <v>50.00577163696289</v>
       </c>
       <c r="F3" t="n">
-        <v>5.077283098638796</v>
+        <v>5.077139341010465</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -620,28 +620,28 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L3" t="n">
-        <v>78.57412092513516</v>
+        <v>82.64878673439914</v>
       </c>
       <c r="M3" t="n">
-        <v>23.07797321490169</v>
+        <v>22.98966487340354</v>
       </c>
       <c r="N3" t="n">
-        <v>314.1315652890347</v>
+        <v>313.3667832967068</v>
       </c>
       <c r="O3" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="P3" t="n">
-        <v>314.145415324007</v>
+        <v>313.5528141633909</v>
       </c>
       <c r="Q3" t="b">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>74.98797783055518</v>
+        <v>73.64119121210271</v>
       </c>
     </row>
     <row r="4">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>50.0062370300293</v>
+        <v>50.01202774047852</v>
       </c>
       <c r="D4" t="n">
-        <v>50.01009368896484</v>
+        <v>50.00724029541016</v>
       </c>
       <c r="E4" t="n">
-        <v>50.1011848449707</v>
+        <v>50.20064163208008</v>
       </c>
       <c r="F4" t="n">
-        <v>5.077040422556528</v>
+        <v>5.074272989946442</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -682,28 +682,28 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L4" t="n">
-        <v>78.57949973743237</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="M4" t="n">
-        <v>23.08509910717317</v>
+        <v>23.18476518306866</v>
       </c>
       <c r="N4" t="n">
-        <v>314.1315652890347</v>
+        <v>312.0935691643398</v>
       </c>
       <c r="O4" t="n">
-        <v>314.1592653589793</v>
+        <v>315.6279461454779</v>
       </c>
       <c r="P4" t="n">
-        <v>314.145415324007</v>
+        <v>313.8607576549089</v>
       </c>
       <c r="Q4" t="b">
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>74.98626562594073</v>
+        <v>73.47853133925828</v>
       </c>
     </row>
     <row r="5">
@@ -716,16 +716,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>50.01202774047852</v>
+        <v>50.0062370300293</v>
       </c>
       <c r="D5" t="n">
-        <v>50.00724029541016</v>
+        <v>50.01009368896484</v>
       </c>
       <c r="E5" t="n">
-        <v>50.20064163208008</v>
+        <v>50.1011848449707</v>
       </c>
       <c r="F5" t="n">
-        <v>5.074272989946442</v>
+        <v>5.077040422556528</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -744,28 +744,28 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L5" t="n">
-        <v>78.69586983587868</v>
+        <v>83.23419294311364</v>
       </c>
       <c r="M5" t="n">
-        <v>23.18476518306866</v>
+        <v>23.08509910717317</v>
       </c>
       <c r="N5" t="n">
-        <v>313.8378490533948</v>
+        <v>313.3667832967068</v>
       </c>
       <c r="O5" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="P5" t="n">
-        <v>313.9985572061871</v>
+        <v>313.5528141633909</v>
       </c>
       <c r="Q5" t="b">
         <v>1</v>
       </c>
       <c r="R5" t="n">
-        <v>74.93750591210421</v>
+        <v>73.4544902219437</v>
       </c>
     </row>
     <row r="6">
@@ -809,25 +809,25 @@
         <v>112</v>
       </c>
       <c r="L6" t="n">
-        <v>80.890045133328</v>
+        <v>84.82789715314635</v>
       </c>
       <c r="M6" t="n">
         <v>22.20557489621094</v>
       </c>
       <c r="N6" t="n">
-        <v>314.1592653589793</v>
+        <v>317.2623272318006</v>
       </c>
       <c r="O6" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="P6" t="n">
-        <v>314.1592653589793</v>
+        <v>315.5005861309378</v>
       </c>
       <c r="Q6" t="b">
         <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>74.25189894020868</v>
+        <v>73.11323627210588</v>
       </c>
     </row>
     <row r="7">
@@ -871,25 +871,25 @@
         <v>111</v>
       </c>
       <c r="L7" t="n">
-        <v>80.89730684178663</v>
+        <v>84.83428522776696</v>
       </c>
       <c r="M7" t="n">
         <v>22.20437705089812</v>
       </c>
       <c r="N7" t="n">
-        <v>314.1592653589793</v>
+        <v>317.2623272318006</v>
       </c>
       <c r="O7" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="P7" t="n">
-        <v>314.1592653589793</v>
+        <v>315.5005861309378</v>
       </c>
       <c r="Q7" t="b">
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>74.24958746661571</v>
+        <v>73.11121152955342</v>
       </c>
     </row>
     <row r="8">
@@ -933,25 +933,25 @@
         <v>117</v>
       </c>
       <c r="L8" t="n">
-        <v>82.09356063317179</v>
+        <v>86.28379979319364</v>
       </c>
       <c r="M8" t="n">
         <v>23.9407126811039</v>
       </c>
       <c r="N8" t="n">
-        <v>307.8119344940786</v>
+        <v>304.4916221213158</v>
       </c>
       <c r="O8" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="P8" t="n">
-        <v>310.9855999265289</v>
+        <v>311.1721162730515</v>
       </c>
       <c r="Q8" t="b">
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>73.60213442276216</v>
+        <v>72.27135874941951</v>
       </c>
     </row>
     <row r="9">
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>49.97760772705078</v>
+        <v>50.00939559936523</v>
       </c>
       <c r="D9" t="n">
-        <v>49.99062347412109</v>
+        <v>49.98019409179688</v>
       </c>
       <c r="E9" t="n">
-        <v>51.02518844604492</v>
+        <v>49.07192611694336</v>
       </c>
       <c r="F9" t="n">
-        <v>5.146871843470635</v>
+        <v>5.128755168304507</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -992,28 +992,28 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="L9" t="n">
-        <v>82.63013147238911</v>
+        <v>85.85532572715697</v>
       </c>
       <c r="M9" t="n">
-        <v>24.01048630489806</v>
+        <v>22.05526287112792</v>
       </c>
       <c r="N9" t="n">
-        <v>303.9601468164716</v>
+        <v>317.2623272318006</v>
       </c>
       <c r="O9" t="n">
-        <v>314.1592653589793</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="P9" t="n">
-        <v>309.0597060877255</v>
+        <v>304.3676207653342</v>
       </c>
       <c r="Q9" t="b">
         <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>73.26402314996868</v>
+        <v>71.79222759921925</v>
       </c>
     </row>
     <row r="10">
@@ -1057,25 +1057,25 @@
         <v>110</v>
       </c>
       <c r="L10" t="n">
-        <v>81.88574721673176</v>
+        <v>85.86371882954251</v>
       </c>
       <c r="M10" t="n">
         <v>22.05578207651078</v>
       </c>
       <c r="N10" t="n">
-        <v>314.1592653589793</v>
+        <v>317.2623272318006</v>
       </c>
       <c r="O10" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="P10" t="n">
-        <v>304.7621962677972</v>
+        <v>304.3676207653342</v>
       </c>
       <c r="Q10" t="b">
         <v>1</v>
       </c>
       <c r="R10" t="n">
-        <v>73.13126489455468</v>
+        <v>71.78947004492866</v>
       </c>
     </row>
     <row r="11">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>50.00939559936523</v>
+        <v>49.97760772705078</v>
       </c>
       <c r="D11" t="n">
-        <v>49.98019409179688</v>
+        <v>49.99062347412109</v>
       </c>
       <c r="E11" t="n">
-        <v>49.07192611694336</v>
+        <v>51.02518844604492</v>
       </c>
       <c r="F11" t="n">
-        <v>5.128755168304507</v>
+        <v>5.146871843470635</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -1116,28 +1116,28 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="L11" t="n">
-        <v>81.8895033996283</v>
+        <v>87.79940414161152</v>
       </c>
       <c r="M11" t="n">
-        <v>22.05526287112792</v>
+        <v>24.01048630489806</v>
       </c>
       <c r="N11" t="n">
-        <v>314.1592653589793</v>
+        <v>300.5870753959373</v>
       </c>
       <c r="O11" t="n">
-        <v>295.365127176615</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="P11" t="n">
-        <v>304.7621962677972</v>
+        <v>309.2198429103623</v>
       </c>
       <c r="Q11" t="b">
         <v>1</v>
       </c>
       <c r="R11" t="n">
-        <v>73.13003239822065</v>
+        <v>71.60615460015511</v>
       </c>
     </row>
     <row r="12">
@@ -1181,25 +1181,25 @@
         <v>108</v>
       </c>
       <c r="L12" t="n">
-        <v>82.71263007328757</v>
+        <v>86.76001954747389</v>
       </c>
       <c r="M12" t="n">
         <v>21.94782072785498</v>
       </c>
       <c r="N12" t="n">
-        <v>314.1592653589793</v>
+        <v>318.6565806888216</v>
       </c>
       <c r="O12" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="P12" t="n">
-        <v>304.7621962677972</v>
+        <v>305.0647474938447</v>
       </c>
       <c r="Q12" t="b">
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>72.85994421676655</v>
+        <v>71.56012936262836</v>
       </c>
     </row>
     <row r="13">
@@ -1243,25 +1243,25 @@
         <v>107</v>
       </c>
       <c r="L13" t="n">
-        <v>86.40674033045698</v>
+        <v>90.17524071230476</v>
       </c>
       <c r="M13" t="n">
         <v>21.56336952220803</v>
       </c>
       <c r="N13" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0898230931229</v>
       </c>
       <c r="O13" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="P13" t="n">
-        <v>304.7621962677972</v>
+        <v>304.7813686959953</v>
       </c>
       <c r="Q13" t="b">
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>71.64781544803849</v>
+        <v>70.41313873675455</v>
       </c>
     </row>
     <row r="14">
@@ -1305,25 +1305,25 @@
         <v>106</v>
       </c>
       <c r="L14" t="n">
-        <v>89.22066299370901</v>
+        <v>92.49349973125699</v>
       </c>
       <c r="M14" t="n">
         <v>21.33079022720709</v>
       </c>
       <c r="N14" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="O14" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P14" t="n">
-        <v>304.5723938501621</v>
+        <v>304.4494200139172</v>
       </c>
       <c r="Q14" t="b">
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>70.70625414672278</v>
+        <v>69.61941995914171</v>
       </c>
     </row>
     <row r="15">
@@ -1367,25 +1367,25 @@
         <v>105</v>
       </c>
       <c r="L15" t="n">
-        <v>89.22175764386837</v>
+        <v>92.55685964381007</v>
       </c>
       <c r="M15" t="n">
         <v>21.33070621721431</v>
       </c>
       <c r="N15" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="O15" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P15" t="n">
-        <v>304.5723938501621</v>
+        <v>304.4494200139172</v>
       </c>
       <c r="Q15" t="b">
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>70.70589474114911</v>
+        <v>69.59860864915458</v>
       </c>
     </row>
     <row r="16">
@@ -1398,16 +1398,16 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>50.01082992553711</v>
+        <v>50.01084136962891</v>
       </c>
       <c r="D16" t="n">
-        <v>50.00517272949219</v>
+        <v>50.00516510009766</v>
       </c>
       <c r="E16" t="n">
-        <v>48.32762145996094</v>
+        <v>48.3272819519043</v>
       </c>
       <c r="F16" t="n">
-        <v>5.223975844398346</v>
+        <v>5.224027531623938</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1426,28 +1426,28 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L16" t="n">
-        <v>89.48990858379221</v>
+        <v>92.85329899001819</v>
       </c>
       <c r="M16" t="n">
-        <v>21.31026858509034</v>
+        <v>21.30992879854643</v>
       </c>
       <c r="N16" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="O16" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P16" t="n">
-        <v>304.5723938501621</v>
+        <v>304.4494200139172</v>
       </c>
       <c r="Q16" t="b">
         <v>1</v>
       </c>
       <c r="R16" t="n">
-        <v>70.61785296673413</v>
+        <v>69.50123965229639</v>
       </c>
     </row>
     <row r="17">
@@ -1460,16 +1460,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>50.01084136962891</v>
+        <v>50.01082992553711</v>
       </c>
       <c r="D17" t="n">
-        <v>50.00516510009766</v>
+        <v>50.00517272949219</v>
       </c>
       <c r="E17" t="n">
-        <v>48.3272819519043</v>
+        <v>48.32762145996094</v>
       </c>
       <c r="F17" t="n">
-        <v>5.224027531623938</v>
+        <v>5.223975844398346</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1488,28 +1488,28 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" t="n">
-        <v>89.49439391321327</v>
+        <v>92.85765641186558</v>
       </c>
       <c r="M17" t="n">
-        <v>21.30992879854643</v>
+        <v>21.31026858509034</v>
       </c>
       <c r="N17" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="O17" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P17" t="n">
-        <v>304.5723938501621</v>
+        <v>304.4494200139172</v>
       </c>
       <c r="Q17" t="b">
         <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>70.61638030226696</v>
+        <v>69.49980840573755</v>
       </c>
     </row>
     <row r="18">
@@ -1553,25 +1553,25 @@
         <v>102</v>
       </c>
       <c r="L18" t="n">
-        <v>90.05582729134076</v>
+        <v>93.25224740780769</v>
       </c>
       <c r="M18" t="n">
         <v>21.26794595147465</v>
       </c>
       <c r="N18" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="O18" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P18" t="n">
-        <v>304.5723938501621</v>
+        <v>304.4494200139172</v>
       </c>
       <c r="Q18" t="b">
         <v>1</v>
       </c>
       <c r="R18" t="n">
-        <v>70.43204534957138</v>
+        <v>69.3702003427877</v>
       </c>
     </row>
     <row r="19">
@@ -1615,25 +1615,25 @@
         <v>101</v>
       </c>
       <c r="L19" t="n">
-        <v>93.64567667079508</v>
+        <v>96.35646782615883</v>
       </c>
       <c r="M19" t="n">
         <v>21.0213146383342</v>
       </c>
       <c r="N19" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839805802706</v>
       </c>
       <c r="O19" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P19" t="n">
-        <v>304.5723938501621</v>
+        <v>306.958756182384</v>
       </c>
       <c r="Q19" t="b">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>69.2533930974502</v>
+        <v>68.6093112232618</v>
       </c>
     </row>
     <row r="20">
@@ -1677,25 +1677,25 @@
         <v>100</v>
       </c>
       <c r="L20" t="n">
-        <v>102.5023719492844</v>
+        <v>105.5763520686886</v>
       </c>
       <c r="M20" t="n">
         <v>20.51886035015927</v>
       </c>
       <c r="N20" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3452100740342</v>
       </c>
       <c r="O20" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="P20" t="n">
-        <v>304.5723938501621</v>
+        <v>304.2393709292659</v>
       </c>
       <c r="Q20" t="b">
         <v>1</v>
       </c>
       <c r="R20" t="n">
-        <v>66.34548172487635</v>
+        <v>65.2982611204404</v>
       </c>
     </row>
     <row r="21">
@@ -1739,25 +1739,25 @@
         <v>119</v>
       </c>
       <c r="L21" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
       <c r="M21" t="n">
         <v>25.59908401827341</v>
       </c>
       <c r="N21" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="O21" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="P21" t="n">
-        <v>283.7842564896719</v>
+        <v>286.159069898802</v>
       </c>
       <c r="Q21" t="b">
         <v>1</v>
       </c>
       <c r="R21" t="n">
-        <v>62.80398946846047</v>
+        <v>62.49068936897628</v>
       </c>
     </row>
     <row r="22">
@@ -1770,16 +1770,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>49.98097991943359</v>
+        <v>50.0217399597168</v>
       </c>
       <c r="D22" t="n">
-        <v>49.98300552368164</v>
+        <v>49.97473907470703</v>
       </c>
       <c r="E22" t="n">
-        <v>52.78891372680664</v>
+        <v>47.35205459594727</v>
       </c>
       <c r="F22" t="n">
-        <v>5.485273489088799</v>
+        <v>5.429960712694054</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1798,28 +1798,28 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>120</v>
+        <v>99</v>
       </c>
       <c r="L22" t="n">
-        <v>109.3492294622752</v>
+        <v>108.5548647407316</v>
       </c>
       <c r="M22" t="n">
-        <v>25.7742803709046</v>
+        <v>20.33364966955584</v>
       </c>
       <c r="N22" t="n">
-        <v>253.4092476203645</v>
+        <v>317.3452100740342</v>
       </c>
       <c r="O22" t="n">
-        <v>314.1592653589793</v>
+        <v>237.416804129758</v>
       </c>
       <c r="P22" t="n">
-        <v>283.7842564896719</v>
+        <v>277.3810071018961</v>
       </c>
       <c r="Q22" t="b">
         <v>1</v>
       </c>
       <c r="R22" t="n">
-        <v>61.46747856456412</v>
+        <v>60.86434832906424</v>
       </c>
     </row>
     <row r="23">
@@ -1832,16 +1832,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>50.0217399597168</v>
+        <v>49.98097991943359</v>
       </c>
       <c r="D23" t="n">
-        <v>49.97473907470703</v>
+        <v>49.98300552368164</v>
       </c>
       <c r="E23" t="n">
-        <v>47.35205459594727</v>
+        <v>52.78891372680664</v>
       </c>
       <c r="F23" t="n">
-        <v>5.429960712694054</v>
+        <v>5.485273489088799</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1860,28 +1860,28 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="L23" t="n">
-        <v>106.2771300804204</v>
+        <v>113.8706623951545</v>
       </c>
       <c r="M23" t="n">
-        <v>20.33364966955584</v>
+        <v>25.7742803709046</v>
       </c>
       <c r="N23" t="n">
-        <v>314.1592653589793</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="O23" t="n">
-        <v>234.9184160202003</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="P23" t="n">
-        <v>274.5388406895898</v>
+        <v>286.159069898802</v>
       </c>
       <c r="Q23" t="b">
         <v>1</v>
       </c>
       <c r="R23" t="n">
-        <v>61.28885449742838</v>
+        <v>60.20721536611649</v>
       </c>
     </row>
     <row r="24">
@@ -1925,25 +1925,25 @@
         <v>121</v>
       </c>
       <c r="L24" t="n">
-        <v>110.149534732799</v>
+        <v>114.6667286416566</v>
       </c>
       <c r="M24" t="n">
         <v>25.81013865404872</v>
       </c>
       <c r="N24" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="O24" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="P24" t="n">
-        <v>283.7842564896719</v>
+        <v>286.159069898802</v>
       </c>
       <c r="Q24" t="b">
         <v>1</v>
       </c>
       <c r="R24" t="n">
-        <v>61.18546670089579</v>
+        <v>59.92902525081328</v>
       </c>
     </row>
     <row r="25">
@@ -1987,25 +1987,25 @@
         <v>98</v>
       </c>
       <c r="L25" t="n">
-        <v>113.243490844349</v>
+        <v>115.2550096237926</v>
       </c>
       <c r="M25" t="n">
         <v>20.02308118569522</v>
       </c>
       <c r="N25" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="O25" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="P25" t="n">
-        <v>274.5388406895898</v>
+        <v>276.8969199909432</v>
       </c>
       <c r="Q25" t="b">
         <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>58.75137719679201</v>
+        <v>58.37620381347599</v>
       </c>
     </row>
     <row r="26">
@@ -2049,25 +2049,25 @@
         <v>97</v>
       </c>
       <c r="L26" t="n">
-        <v>113.7748396201627</v>
+        <v>117.1992547452434</v>
       </c>
       <c r="M26" t="n">
         <v>20.00072847985969</v>
       </c>
       <c r="N26" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="O26" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="P26" t="n">
-        <v>274.5388406895898</v>
+        <v>276.8969199909432</v>
       </c>
       <c r="Q26" t="b">
         <v>1</v>
       </c>
       <c r="R26" t="n">
-        <v>58.5578349007442</v>
+        <v>57.67404897494824</v>
       </c>
     </row>
     <row r="27">
@@ -2111,25 +2111,25 @@
         <v>96</v>
       </c>
       <c r="L27" t="n">
-        <v>115.6536624166284</v>
+        <v>118.3273414111442</v>
       </c>
       <c r="M27" t="n">
         <v>19.92271434586333</v>
       </c>
       <c r="N27" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="O27" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="P27" t="n">
-        <v>274.5388406895898</v>
+        <v>276.8969199909432</v>
       </c>
       <c r="Q27" t="b">
         <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>57.87347898529471</v>
+        <v>57.26664586409464</v>
       </c>
     </row>
     <row r="28">
@@ -2173,25 +2173,25 @@
         <v>95</v>
       </c>
       <c r="L28" t="n">
-        <v>120.4741900327024</v>
+        <v>121.9876728255553</v>
       </c>
       <c r="M28" t="n">
         <v>19.73136515540256</v>
       </c>
       <c r="N28" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="O28" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="P28" t="n">
-        <v>274.5388406895898</v>
+        <v>276.8969199909432</v>
       </c>
       <c r="Q28" t="b">
         <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>56.11761536906983</v>
+        <v>55.94473465810118</v>
       </c>
     </row>
     <row r="29">
@@ -2235,25 +2235,25 @@
         <v>94</v>
       </c>
       <c r="L29" t="n">
-        <v>122.9627839138132</v>
+        <v>123.891393669422</v>
       </c>
       <c r="M29" t="n">
         <v>19.63700216854963</v>
       </c>
       <c r="N29" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="O29" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="P29" t="n">
-        <v>274.5388406895898</v>
+        <v>276.8969199909432</v>
       </c>
       <c r="Q29" t="b">
         <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>55.21115205230929</v>
+        <v>55.25721496885041</v>
       </c>
     </row>
     <row r="30">
@@ -2297,25 +2297,25 @@
         <v>93</v>
       </c>
       <c r="L30" t="n">
-        <v>127.7892139266595</v>
+        <v>128.6927136711962</v>
       </c>
       <c r="M30" t="n">
         <v>19.46117051643042</v>
       </c>
       <c r="N30" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0867669719897</v>
       </c>
       <c r="O30" t="n">
-        <v>231.9376528434134</v>
+        <v>234.0298894599115</v>
       </c>
       <c r="P30" t="n">
-        <v>273.0484591011963</v>
+        <v>276.0583282159506</v>
       </c>
       <c r="Q30" t="b">
         <v>1</v>
       </c>
       <c r="R30" t="n">
-        <v>53.19907156872154</v>
+        <v>53.38205715332578</v>
       </c>
     </row>
     <row r="31">
@@ -2359,25 +2359,25 @@
         <v>92</v>
       </c>
       <c r="L31" t="n">
-        <v>133.5845032849845</v>
+        <v>136.4629930245137</v>
       </c>
       <c r="M31" t="n">
         <v>19.25962938677999</v>
       </c>
       <c r="N31" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0867669719897</v>
       </c>
       <c r="O31" t="n">
-        <v>231.9376528434134</v>
+        <v>234.0298894599115</v>
       </c>
       <c r="P31" t="n">
-        <v>273.0484591011963</v>
+        <v>276.0583282159506</v>
       </c>
       <c r="Q31" t="b">
         <v>1</v>
       </c>
       <c r="R31" t="n">
-        <v>51.07663169947577</v>
+        <v>50.56733339420809</v>
       </c>
     </row>
     <row r="32">
@@ -2390,16 +2390,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>50.01002502441406</v>
+        <v>49.97886276245117</v>
       </c>
       <c r="D32" t="n">
-        <v>50.0036506652832</v>
+        <v>49.98746490478516</v>
       </c>
       <c r="E32" t="n">
-        <v>53.79951477050781</v>
+        <v>45.9925651550293</v>
       </c>
       <c r="F32" t="n">
-        <v>5.800569750334801</v>
+        <v>5.86172714950602</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -2418,28 +2418,28 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="L32" t="n">
-        <v>135.9921309828678</v>
+        <v>144.7702614025382</v>
       </c>
       <c r="M32" t="n">
-        <v>26.78601134579059</v>
+        <v>18.97085198283127</v>
       </c>
       <c r="N32" t="n">
-        <v>225.0251857356426</v>
+        <v>316.240549678392</v>
       </c>
       <c r="O32" t="n">
-        <v>314.1592653589793</v>
+        <v>234.0298894599115</v>
       </c>
       <c r="P32" t="n">
-        <v>269.5922255473109</v>
+        <v>275.1352195691518</v>
       </c>
       <c r="Q32" t="b">
         <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>49.55636027456494</v>
+        <v>47.38214117798467</v>
       </c>
     </row>
     <row r="33">
@@ -2452,16 +2452,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>50.01501846313477</v>
+        <v>49.98307800292969</v>
       </c>
       <c r="D33" t="n">
-        <v>50.00498962402344</v>
+        <v>49.9872932434082</v>
       </c>
       <c r="E33" t="n">
-        <v>53.81509017944336</v>
+        <v>45.94309234619141</v>
       </c>
       <c r="F33" t="n">
-        <v>5.802767461220163</v>
+        <v>5.883107584952053</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -2480,28 +2480,28 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="L33" t="n">
-        <v>136.4631495273463</v>
+        <v>144.8424016943108</v>
       </c>
       <c r="M33" t="n">
-        <v>26.80242233614081</v>
+        <v>18.92119962604703</v>
       </c>
       <c r="N33" t="n">
-        <v>225.0251857356426</v>
+        <v>316.240549678392</v>
       </c>
       <c r="O33" t="n">
-        <v>314.1592653589793</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="P33" t="n">
-        <v>269.5922255473109</v>
+        <v>258.8896387480423</v>
       </c>
       <c r="Q33" t="b">
         <v>1</v>
       </c>
       <c r="R33" t="n">
-        <v>49.38164509369417</v>
+        <v>44.05245324040374</v>
       </c>
     </row>
     <row r="34">
@@ -2514,16 +2514,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>49.97886276245117</v>
+        <v>49.98400115966797</v>
       </c>
       <c r="D34" t="n">
-        <v>49.98746490478516</v>
+        <v>49.9875373840332</v>
       </c>
       <c r="E34" t="n">
-        <v>45.9925651550293</v>
+        <v>45.74578857421875</v>
       </c>
       <c r="F34" t="n">
-        <v>5.86172714950602</v>
+        <v>5.960326539852002</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -2542,28 +2542,28 @@
         </is>
       </c>
       <c r="K34" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L34" t="n">
-        <v>142.4192832986008</v>
+        <v>152.1045352101532</v>
       </c>
       <c r="M34" t="n">
-        <v>18.97085198283127</v>
+        <v>18.72389354337939</v>
       </c>
       <c r="N34" t="n">
-        <v>314.1592653589793</v>
+        <v>316.240549678392</v>
       </c>
       <c r="O34" t="n">
-        <v>231.9376528434134</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="P34" t="n">
-        <v>273.0484591011963</v>
+        <v>258.8896387480423</v>
       </c>
       <c r="Q34" t="b">
         <v>1</v>
       </c>
       <c r="R34" t="n">
-        <v>47.84102288384721</v>
+        <v>41.24734541493761</v>
       </c>
     </row>
     <row r="35">
@@ -2576,16 +2576,16 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>49.98307800292969</v>
+        <v>50.01002502441406</v>
       </c>
       <c r="D35" t="n">
-        <v>49.9872932434082</v>
+        <v>50.0036506652832</v>
       </c>
       <c r="E35" t="n">
-        <v>45.94309234619141</v>
+        <v>53.79951477050781</v>
       </c>
       <c r="F35" t="n">
-        <v>5.883107584952053</v>
+        <v>5.800569750334801</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -2604,28 +2604,28 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="L35" t="n">
-        <v>143.991974532357</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="M35" t="n">
-        <v>18.92119962604703</v>
+        <v>26.78601134579059</v>
       </c>
       <c r="N35" t="n">
-        <v>314.1592653589793</v>
+        <v>227.8527994053118</v>
       </c>
       <c r="O35" t="n">
-        <v>195.3400059676167</v>
+        <v>316.2687233454461</v>
       </c>
       <c r="P35" t="n">
-        <v>254.749635663298</v>
+        <v>272.0607613753789</v>
       </c>
       <c r="Q35" t="b">
         <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>43.4770636050405</v>
+        <v>40.34212048347412</v>
       </c>
     </row>
     <row r="36">
@@ -2638,16 +2638,16 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>49.98400115966797</v>
+        <v>50.01501846313477</v>
       </c>
       <c r="D36" t="n">
-        <v>49.9875373840332</v>
+        <v>50.00498962402344</v>
       </c>
       <c r="E36" t="n">
-        <v>45.74578857421875</v>
+        <v>53.81509017944336</v>
       </c>
       <c r="F36" t="n">
-        <v>5.960326539852002</v>
+        <v>5.802767461220163</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -2666,28 +2666,28 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="L36" t="n">
-        <v>150.422316992052</v>
+        <v>162.8648876385568</v>
       </c>
       <c r="M36" t="n">
-        <v>18.72389354337939</v>
+        <v>26.80242233614081</v>
       </c>
       <c r="N36" t="n">
-        <v>314.1592653589793</v>
+        <v>227.8527994053118</v>
       </c>
       <c r="O36" t="n">
-        <v>195.3400059676167</v>
+        <v>316.2687233454461</v>
       </c>
       <c r="P36" t="n">
-        <v>254.749635663298</v>
+        <v>272.0607613753789</v>
       </c>
       <c r="Q36" t="b">
         <v>1</v>
       </c>
       <c r="R36" t="n">
-        <v>40.95288238572211</v>
+        <v>40.13657580931265</v>
       </c>
     </row>
     <row r="37">
@@ -2731,25 +2731,25 @@
         <v>88</v>
       </c>
       <c r="L37" t="n">
-        <v>156.2610422305858</v>
+        <v>158.173188195218</v>
       </c>
       <c r="M37" t="n">
         <v>18.55057658193569</v>
       </c>
       <c r="N37" t="n">
-        <v>314.1592653589793</v>
+        <v>316.248869489448</v>
       </c>
       <c r="O37" t="n">
-        <v>195.3400059676167</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="P37" t="n">
-        <v>254.749635663298</v>
+        <v>258.8937986535703</v>
       </c>
       <c r="Q37" t="b">
         <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>38.66093593275413</v>
+        <v>38.90421902037446</v>
       </c>
     </row>
     <row r="38">
@@ -2793,25 +2793,25 @@
         <v>87</v>
       </c>
       <c r="L38" t="n">
-        <v>167.6902340874137</v>
+        <v>170.0510698939867</v>
       </c>
       <c r="M38" t="n">
         <v>18.22466888902203</v>
       </c>
       <c r="N38" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2260680509127</v>
       </c>
       <c r="O38" t="n">
-        <v>191.753677956091</v>
+        <v>197.8936699667733</v>
       </c>
       <c r="P38" t="n">
-        <v>252.9564716575352</v>
+        <v>257.059869008843</v>
       </c>
       <c r="Q38" t="b">
         <v>1</v>
       </c>
       <c r="R38" t="n">
-        <v>33.70786958380692</v>
+        <v>33.84767892800225</v>
       </c>
     </row>
     <row r="39">
@@ -2824,16 +2824,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>50.0087776184082</v>
+        <v>49.99313354492188</v>
       </c>
       <c r="D39" t="n">
-        <v>49.98618698120117</v>
+        <v>50.00785064697266</v>
       </c>
       <c r="E39" t="n">
-        <v>45.02943420410156</v>
+        <v>54.98001098632812</v>
       </c>
       <c r="F39" t="n">
-        <v>6.249239044883462</v>
+        <v>6.251092442842805</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2852,28 +2852,28 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="L39" t="n">
-        <v>175.6268913642302</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="M39" t="n">
-        <v>18.00647863107158</v>
+        <v>27.96755220933544</v>
       </c>
       <c r="N39" t="n">
-        <v>314.1592653589793</v>
+        <v>178.7889751279239</v>
       </c>
       <c r="O39" t="n">
-        <v>175.9755522072987</v>
+        <v>316.3449265579602</v>
       </c>
       <c r="P39" t="n">
-        <v>245.067408783139</v>
+        <v>247.566950842942</v>
       </c>
       <c r="Q39" t="b">
         <v>1</v>
       </c>
       <c r="R39" t="n">
-        <v>28.335272227225</v>
+        <v>28.19805815652953</v>
       </c>
     </row>
     <row r="40">
@@ -2886,16 +2886,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>49.99313354492188</v>
+        <v>50.0087776184082</v>
       </c>
       <c r="D40" t="n">
-        <v>50.00785064697266</v>
+        <v>49.98618698120117</v>
       </c>
       <c r="E40" t="n">
-        <v>54.98001098632812</v>
+        <v>45.02943420410156</v>
       </c>
       <c r="F40" t="n">
-        <v>6.251092442842805</v>
+        <v>6.249239044883462</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2914,28 +2914,28 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="L40" t="n">
-        <v>175.9755522072987</v>
+        <v>178.7889751279239</v>
       </c>
       <c r="M40" t="n">
-        <v>27.96755220933544</v>
+        <v>18.00647863107158</v>
       </c>
       <c r="N40" t="n">
-        <v>175.6268913642302</v>
+        <v>316.336112816567</v>
       </c>
       <c r="O40" t="n">
-        <v>314.1592653589793</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P40" t="n">
-        <v>244.8930783616048</v>
+        <v>247.0469954422347</v>
       </c>
       <c r="Q40" t="b">
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>28.14188404808391</v>
+        <v>27.62956909964569</v>
       </c>
     </row>
     <row r="41">
@@ -2979,25 +2979,25 @@
         <v>85</v>
       </c>
       <c r="L41" t="n">
-        <v>179.3146318707147</v>
+        <v>181.1452928466024</v>
       </c>
       <c r="M41" t="n">
         <v>17.90678845231076</v>
       </c>
       <c r="N41" t="n">
-        <v>314.1592653589793</v>
+        <v>316.346243104606</v>
       </c>
       <c r="O41" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P41" t="n">
-        <v>245.067408783139</v>
+        <v>247.0520605862542</v>
       </c>
       <c r="Q41" t="b">
         <v>1</v>
       </c>
       <c r="R41" t="n">
-        <v>26.83048604419252</v>
+        <v>26.67727910597271</v>
       </c>
     </row>
     <row r="42">
@@ -3041,25 +3041,25 @@
         <v>84</v>
       </c>
       <c r="L42" t="n">
-        <v>180.5367905217445</v>
+        <v>183.2890629174703</v>
       </c>
       <c r="M42" t="n">
         <v>17.87404206044399</v>
       </c>
       <c r="N42" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3463324831218</v>
       </c>
       <c r="O42" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P42" t="n">
-        <v>245.067408783139</v>
+        <v>247.0521052755121</v>
       </c>
       <c r="Q42" t="b">
         <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>26.33178299057213</v>
+        <v>25.80955231566772</v>
       </c>
     </row>
     <row r="43">
@@ -3103,25 +3103,25 @@
         <v>83</v>
       </c>
       <c r="L43" t="n">
-        <v>191.4538906498383</v>
+        <v>194.3516413732588</v>
       </c>
       <c r="M43" t="n">
         <v>17.58484373713333</v>
       </c>
       <c r="N43" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O43" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P43" t="n">
-        <v>245.067408783139</v>
+        <v>247.1049060420578</v>
       </c>
       <c r="Q43" t="b">
         <v>1</v>
       </c>
       <c r="R43" t="n">
-        <v>21.87704942061206</v>
+        <v>21.34852986683328</v>
       </c>
     </row>
     <row r="44">
@@ -3165,25 +3165,25 @@
         <v>82</v>
       </c>
       <c r="L44" t="n">
-        <v>194.6181629775267</v>
+        <v>198.0488042536388</v>
       </c>
       <c r="M44" t="n">
         <v>17.50216119115977</v>
       </c>
       <c r="N44" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O44" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P44" t="n">
-        <v>245.067408783139</v>
+        <v>247.1049060420578</v>
       </c>
       <c r="Q44" t="b">
         <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>20.58586494879659</v>
+        <v>19.8523382534823</v>
       </c>
     </row>
     <row r="45">
@@ -3196,16 +3196,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>49.9990348815918</v>
+        <v>49.99614334106445</v>
       </c>
       <c r="D45" t="n">
-        <v>49.99960327148438</v>
+        <v>49.99660110473633</v>
       </c>
       <c r="E45" t="n">
-        <v>55.39908981323242</v>
+        <v>44.45116424560547</v>
       </c>
       <c r="F45" t="n">
-        <v>6.427142298255871</v>
+        <v>6.493680333796546</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -3224,28 +3224,28 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="L45" t="n">
-        <v>191.753677956091</v>
+        <v>199.53895674502</v>
       </c>
       <c r="M45" t="n">
-        <v>28.38675372190001</v>
+        <v>17.42690535234424</v>
       </c>
       <c r="N45" t="n">
-        <v>167.6902340874137</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O45" t="n">
-        <v>314.1592653589793</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P45" t="n">
-        <v>240.9247497231965</v>
+        <v>247.1049060420578</v>
       </c>
       <c r="Q45" t="b">
         <v>1</v>
       </c>
       <c r="R45" t="n">
-        <v>20.40930698220053</v>
+        <v>19.24929377522837</v>
       </c>
     </row>
     <row r="46">
@@ -3258,16 +3258,16 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>49.99614334106445</v>
+        <v>49.99613189697266</v>
       </c>
       <c r="D46" t="n">
-        <v>49.99660110473633</v>
+        <v>49.99661254882812</v>
       </c>
       <c r="E46" t="n">
-        <v>44.45116424560547</v>
+        <v>44.45056533813477</v>
       </c>
       <c r="F46" t="n">
-        <v>6.493680333796546</v>
+        <v>6.493943615798817</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -3286,28 +3286,28 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="L46" t="n">
-        <v>197.5050285414572</v>
+        <v>199.560790903416</v>
       </c>
       <c r="M46" t="n">
-        <v>17.42690535234424</v>
+        <v>17.42630622623654</v>
       </c>
       <c r="N46" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O46" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P46" t="n">
-        <v>245.067408783139</v>
+        <v>247.1049060420578</v>
       </c>
       <c r="Q46" t="b">
         <v>1</v>
       </c>
       <c r="R46" t="n">
-        <v>19.4078765829568</v>
+        <v>19.2404577878149</v>
       </c>
     </row>
     <row r="47">
@@ -3320,16 +3320,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>49.99613189697266</v>
+        <v>49.9990348815918</v>
       </c>
       <c r="D47" t="n">
-        <v>49.99661254882812</v>
+        <v>49.99960327148438</v>
       </c>
       <c r="E47" t="n">
-        <v>44.45056533813477</v>
+        <v>55.39908981323242</v>
       </c>
       <c r="F47" t="n">
-        <v>6.493943615798817</v>
+        <v>6.427142298255871</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -3348,28 +3348,28 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="L47" t="n">
-        <v>197.5281152127406</v>
+        <v>197.8936699667733</v>
       </c>
       <c r="M47" t="n">
-        <v>17.42630622623654</v>
+        <v>28.38675372190001</v>
       </c>
       <c r="N47" t="n">
-        <v>314.1592653589793</v>
+        <v>170.0510698939867</v>
       </c>
       <c r="O47" t="n">
-        <v>175.9755522072987</v>
+        <v>316.4511346509275</v>
       </c>
       <c r="P47" t="n">
-        <v>245.067408783139</v>
+        <v>243.2511022724571</v>
       </c>
       <c r="Q47" t="b">
         <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>19.39845604376798</v>
+        <v>18.64634194129181</v>
       </c>
     </row>
     <row r="48">
@@ -3413,25 +3413,25 @@
         <v>79</v>
       </c>
       <c r="L48" t="n">
-        <v>198.4697210122667</v>
+        <v>202.162792105526</v>
       </c>
       <c r="M48" t="n">
         <v>17.40188338525257</v>
       </c>
       <c r="N48" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O48" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="P48" t="n">
-        <v>245.067408783139</v>
+        <v>247.1049060420578</v>
       </c>
       <c r="Q48" t="b">
         <v>1</v>
       </c>
       <c r="R48" t="n">
-        <v>19.01423286035833</v>
+        <v>18.1874632342923</v>
       </c>
     </row>
     <row r="49">
@@ -3444,16 +3444,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>49.99726867675781</v>
+        <v>49.99241638183594</v>
       </c>
       <c r="D49" t="n">
-        <v>50.01203155517578</v>
+        <v>49.99889373779297</v>
       </c>
       <c r="E49" t="n">
-        <v>55.49259948730469</v>
+        <v>44.38333129882812</v>
       </c>
       <c r="F49" t="n">
-        <v>6.462461677039332</v>
+        <v>6.521479418986281</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -3472,28 +3472,28 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="L49" t="n">
-        <v>195.3400059676167</v>
+        <v>203.3757378729639</v>
       </c>
       <c r="M49" t="n">
-        <v>28.48110222936108</v>
+        <v>17.35889927591647</v>
       </c>
       <c r="N49" t="n">
-        <v>156.2610422305858</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O49" t="n">
-        <v>314.1592653589793</v>
+        <v>162.8648876385568</v>
       </c>
       <c r="P49" t="n">
-        <v>235.2101537947826</v>
+        <v>239.658410827385</v>
       </c>
       <c r="Q49" t="b">
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>16.95086168004123</v>
+        <v>15.13932802490034</v>
       </c>
     </row>
     <row r="50">
@@ -3506,16 +3506,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>49.99241638183594</v>
+        <v>49.99726867675781</v>
       </c>
       <c r="D50" t="n">
-        <v>49.99889373779297</v>
+        <v>50.01203155517578</v>
       </c>
       <c r="E50" t="n">
-        <v>44.38333129882812</v>
+        <v>55.49259948730469</v>
       </c>
       <c r="F50" t="n">
-        <v>6.521479418986281</v>
+        <v>6.462461677039332</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3534,28 +3534,28 @@
         </is>
       </c>
       <c r="K50" t="n">
-        <v>78</v>
+        <v>126</v>
       </c>
       <c r="L50" t="n">
-        <v>200.1233890670008</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="M50" t="n">
-        <v>17.35889927591647</v>
+        <v>28.48110222936108</v>
       </c>
       <c r="N50" t="n">
-        <v>314.1592653589793</v>
+        <v>158.173188195218</v>
       </c>
       <c r="O50" t="n">
-        <v>136.4631495273463</v>
+        <v>316.4511346509275</v>
       </c>
       <c r="P50" t="n">
-        <v>225.3112074431628</v>
+        <v>237.3121614230728</v>
       </c>
       <c r="Q50" t="b">
         <v>1</v>
       </c>
       <c r="R50" t="n">
-        <v>11.17912360507674</v>
+        <v>15.0744207085133</v>
       </c>
     </row>
     <row r="51">
@@ -3599,25 +3599,25 @@
         <v>77</v>
       </c>
       <c r="L51" t="n">
-        <v>201.9262946834099</v>
+        <v>204.0270110073141</v>
       </c>
       <c r="M51" t="n">
         <v>17.31215272078115</v>
       </c>
       <c r="N51" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="O51" t="n">
-        <v>136.4631495273463</v>
+        <v>162.8648876385568</v>
       </c>
       <c r="P51" t="n">
-        <v>225.3112074431628</v>
+        <v>239.658410827385</v>
       </c>
       <c r="Q51" t="b">
         <v>1</v>
       </c>
       <c r="R51" t="n">
-        <v>10.37893899070779</v>
+        <v>14.86757743951432</v>
       </c>
     </row>
     <row r="52">
@@ -3661,25 +3661,25 @@
         <v>76</v>
       </c>
       <c r="L52" t="n">
-        <v>213.719050856379</v>
+        <v>215.8886209778705</v>
       </c>
       <c r="M52" t="n">
         <v>17.00823357096455</v>
       </c>
       <c r="N52" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5778275061289</v>
       </c>
       <c r="O52" t="n">
-        <v>136.4631495273463</v>
+        <v>162.8648876385568</v>
       </c>
       <c r="P52" t="n">
-        <v>225.3112074431628</v>
+        <v>239.7213575723429</v>
       </c>
       <c r="Q52" t="b">
         <v>1</v>
       </c>
       <c r="R52" t="n">
-        <v>5.144953381738926</v>
+        <v>9.941849502199728</v>
       </c>
     </row>
     <row r="53">
@@ -3723,25 +3723,25 @@
         <v>75</v>
       </c>
       <c r="L53" t="n">
-        <v>225.0251857356426</v>
+        <v>227.8527994053118</v>
       </c>
       <c r="M53" t="n">
         <v>16.71625580393347</v>
       </c>
       <c r="N53" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5626661416117</v>
       </c>
       <c r="O53" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="P53" t="n">
-        <v>225.0756981709236</v>
+        <v>239.4341736873391</v>
       </c>
       <c r="Q53" t="b">
         <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02244242079064707</v>
+        <v>4.836976319491749</v>
       </c>
     </row>
     <row r="54">
@@ -3785,25 +3785,25 @@
         <v>74</v>
       </c>
       <c r="L54" t="n">
-        <v>225.0301843118329</v>
+        <v>227.8577603933362</v>
       </c>
       <c r="M54" t="n">
         <v>16.71612588002626</v>
       </c>
       <c r="N54" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5626661416117</v>
       </c>
       <c r="O54" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="P54" t="n">
-        <v>225.0756981709236</v>
+        <v>239.4341736873391</v>
       </c>
       <c r="Q54" t="b">
         <v>1</v>
       </c>
       <c r="R54" t="n">
-        <v>0.02022157854468798</v>
+        <v>4.834904356267799</v>
       </c>
     </row>
     <row r="55">
@@ -3847,25 +3847,25 @@
         <v>73</v>
       </c>
       <c r="L55" t="n">
-        <v>226.2688907452621</v>
+        <v>229.0752350057351</v>
       </c>
       <c r="M55" t="n">
         <v>16.68390388708811</v>
       </c>
       <c r="N55" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6143668288898</v>
       </c>
       <c r="O55" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="P55" t="n">
-        <v>225.0756981709236</v>
+        <v>239.4600240309782</v>
       </c>
       <c r="Q55" t="b">
         <v>1</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.5301294560163594</v>
+        <v>4.336752686494194</v>
       </c>
     </row>
     <row r="56">
@@ -3878,16 +3878,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>49.99188613891602</v>
+        <v>49.98930358886719</v>
       </c>
       <c r="D56" t="n">
-        <v>50.00178527832031</v>
+        <v>50.00143814086914</v>
       </c>
       <c r="E56" t="n">
-        <v>43.60721969604492</v>
+        <v>43.57549285888672</v>
       </c>
       <c r="F56" t="n">
-        <v>6.888341906696954</v>
+        <v>6.902595789911511</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -3906,28 +3906,28 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L56" t="n">
-        <v>230.1589532726078</v>
+        <v>233.4640201931528</v>
       </c>
       <c r="M56" t="n">
-        <v>16.58242677762431</v>
+        <v>16.55059311202909</v>
       </c>
       <c r="N56" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6143668288898</v>
       </c>
       <c r="O56" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="P56" t="n">
-        <v>225.0756981709236</v>
+        <v>239.4600240309782</v>
       </c>
       <c r="Q56" t="b">
         <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.258464660109127</v>
+        <v>2.503968611082108</v>
       </c>
     </row>
     <row r="57">
@@ -3940,16 +3940,16 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>49.98930358886719</v>
+        <v>49.99188613891602</v>
       </c>
       <c r="D57" t="n">
-        <v>50.00143814086914</v>
+        <v>50.00178527832031</v>
       </c>
       <c r="E57" t="n">
-        <v>43.57549285888672</v>
+        <v>43.60721969604492</v>
       </c>
       <c r="F57" t="n">
-        <v>6.902595789911511</v>
+        <v>6.888341906696954</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -3968,28 +3968,28 @@
         </is>
       </c>
       <c r="K57" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="L57" t="n">
-        <v>231.3715413458951</v>
+        <v>233.5399884210641</v>
       </c>
       <c r="M57" t="n">
-        <v>16.55059311202909</v>
+        <v>16.58242677762431</v>
       </c>
       <c r="N57" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6143668288898</v>
       </c>
       <c r="O57" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="P57" t="n">
-        <v>225.0756981709236</v>
+        <v>239.4600240309782</v>
       </c>
       <c r="Q57" t="b">
         <v>1</v>
       </c>
       <c r="R57" t="n">
-        <v>-2.797211438700264</v>
+        <v>2.472243805148966</v>
       </c>
     </row>
     <row r="58">
@@ -4033,25 +4033,25 @@
         <v>70</v>
       </c>
       <c r="L58" t="n">
-        <v>234.6376077615358</v>
+        <v>236.6410918994229</v>
       </c>
       <c r="M58" t="n">
         <v>16.46476130034345</v>
       </c>
       <c r="N58" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6143668288898</v>
       </c>
       <c r="O58" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="P58" t="n">
-        <v>225.0756981709236</v>
+        <v>239.4600240309782</v>
       </c>
       <c r="Q58" t="b">
         <v>1</v>
       </c>
       <c r="R58" t="n">
-        <v>-4.248308310633742</v>
+        <v>1.177203645143965</v>
       </c>
     </row>
     <row r="59">
@@ -4095,25 +4095,25 @@
         <v>127</v>
       </c>
       <c r="L59" t="n">
-        <v>231.9376528434134</v>
+        <v>234.0298894599115</v>
       </c>
       <c r="M59" t="n">
         <v>29.42792490111245</v>
       </c>
       <c r="N59" t="n">
-        <v>127.7892139266595</v>
+        <v>128.6927136711962</v>
       </c>
       <c r="O59" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6194114183377</v>
       </c>
       <c r="P59" t="n">
-        <v>220.9742396428194</v>
+        <v>222.6560625447669</v>
       </c>
       <c r="Q59" t="b">
         <v>1</v>
       </c>
       <c r="R59" t="n">
-        <v>-4.961398766804259</v>
+        <v>-5.108249371318063</v>
       </c>
     </row>
     <row r="60">
@@ -4157,25 +4157,25 @@
         <v>128</v>
       </c>
       <c r="L60" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="M60" t="n">
         <v>29.5064673693055</v>
       </c>
       <c r="N60" t="n">
-        <v>127.7892139266595</v>
+        <v>128.6927136711962</v>
       </c>
       <c r="O60" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6194114183377</v>
       </c>
       <c r="P60" t="n">
-        <v>220.9742396428194</v>
+        <v>222.6560625447669</v>
       </c>
       <c r="Q60" t="b">
         <v>1</v>
       </c>
       <c r="R60" t="n">
-        <v>-6.310317618886296</v>
+        <v>-6.629391275624186</v>
       </c>
     </row>
     <row r="61">
@@ -4219,25 +4219,25 @@
         <v>69</v>
       </c>
       <c r="L61" t="n">
-        <v>251.0139509799078</v>
+        <v>252.5458388685716</v>
       </c>
       <c r="M61" t="n">
         <v>16.02302910766215</v>
       </c>
       <c r="N61" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6418857289111</v>
       </c>
       <c r="O61" t="n">
-        <v>110.149534732799</v>
+        <v>114.6667286416566</v>
       </c>
       <c r="P61" t="n">
-        <v>212.1544000458891</v>
+        <v>215.6543071852838</v>
       </c>
       <c r="Q61" t="b">
         <v>1</v>
       </c>
       <c r="R61" t="n">
-        <v>-18.31663681055558</v>
+        <v>-17.10679103273909</v>
       </c>
     </row>
     <row r="62">
@@ -4281,25 +4281,25 @@
         <v>68</v>
       </c>
       <c r="L62" t="n">
-        <v>251.0332160772647</v>
+        <v>252.5607021558965</v>
       </c>
       <c r="M62" t="n">
         <v>16.02249483210673</v>
       </c>
       <c r="N62" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6418857289111</v>
       </c>
       <c r="O62" t="n">
-        <v>110.149534732799</v>
+        <v>114.6667286416566</v>
       </c>
       <c r="P62" t="n">
-        <v>212.1544000458891</v>
+        <v>215.6543071852838</v>
       </c>
       <c r="Q62" t="b">
         <v>1</v>
       </c>
       <c r="R62" t="n">
-        <v>-18.32571750713916</v>
+        <v>-17.11368321473115</v>
       </c>
     </row>
     <row r="63">
@@ -4343,25 +4343,25 @@
         <v>67</v>
       </c>
       <c r="L63" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="M63" t="n">
         <v>15.95626057567494</v>
       </c>
       <c r="N63" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6357038559812</v>
       </c>
       <c r="O63" t="n">
-        <v>110.149534732799</v>
+        <v>114.6667286416566</v>
       </c>
       <c r="P63" t="n">
-        <v>212.1544000458891</v>
+        <v>215.6512162488189</v>
       </c>
       <c r="Q63" t="b">
         <v>1</v>
       </c>
       <c r="R63" t="n">
-        <v>-19.44567143813747</v>
+        <v>-18.2258095956584</v>
       </c>
     </row>
     <row r="64">
@@ -4405,25 +4405,25 @@
         <v>66</v>
       </c>
       <c r="L64" t="n">
-        <v>286.2196126656559</v>
+        <v>285.0381023203544</v>
       </c>
       <c r="M64" t="n">
         <v>14.92568103876039</v>
       </c>
       <c r="N64" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5930693749811</v>
       </c>
       <c r="O64" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
       <c r="P64" t="n">
-        <v>209.8578436448644</v>
+        <v>211.9646819010855</v>
       </c>
       <c r="Q64" t="b">
         <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>-36.38737904408092</v>
+        <v>-34.47433778301283</v>
       </c>
     </row>
     <row r="65">
@@ -4436,16 +4436,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>49.98761367797852</v>
+        <v>49.99382400512695</v>
       </c>
       <c r="D65" t="n">
-        <v>49.99834060668945</v>
+        <v>50.00798416137695</v>
       </c>
       <c r="E65" t="n">
-        <v>41.8192253112793</v>
+        <v>58.3980712890625</v>
       </c>
       <c r="F65" t="n">
-        <v>7.842928419881352</v>
+        <v>7.973911286432147</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -4464,28 +4464,28 @@
         </is>
       </c>
       <c r="K65" t="n">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="L65" t="n">
-        <v>289.6914968457265</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="M65" t="n">
-        <v>14.79381895132253</v>
+        <v>31.38684530632878</v>
       </c>
       <c r="N65" t="n">
-        <v>314.1592653589793</v>
+        <v>92.49349973125699</v>
       </c>
       <c r="O65" t="n">
-        <v>82.63013147238911</v>
+        <v>316.5588351730509</v>
       </c>
       <c r="P65" t="n">
-        <v>198.3946984156842</v>
+        <v>204.5261674521539</v>
       </c>
       <c r="Q65" t="b">
         <v>1</v>
       </c>
       <c r="R65" t="n">
-        <v>-46.0177611393394</v>
+        <v>-42.34537096706912</v>
       </c>
     </row>
     <row r="66">
@@ -4498,16 +4498,16 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>49.99382400512695</v>
+        <v>49.98761367797852</v>
       </c>
       <c r="D66" t="n">
-        <v>50.00798416137695</v>
+        <v>49.99834060668945</v>
       </c>
       <c r="E66" t="n">
-        <v>58.3980712890625</v>
+        <v>41.8192253112793</v>
       </c>
       <c r="F66" t="n">
-        <v>7.973911286432147</v>
+        <v>7.842928419881352</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -4526,28 +4526,28 @@
         </is>
       </c>
       <c r="K66" t="n">
-        <v>129</v>
+        <v>65</v>
       </c>
       <c r="L66" t="n">
-        <v>294.9855223413448</v>
+        <v>288.0497510411172</v>
       </c>
       <c r="M66" t="n">
-        <v>31.38684530632878</v>
+        <v>14.79381895132253</v>
       </c>
       <c r="N66" t="n">
-        <v>89.22066299370901</v>
+        <v>316.5930693749811</v>
       </c>
       <c r="O66" t="n">
-        <v>314.1592653589793</v>
+        <v>87.79940414161152</v>
       </c>
       <c r="P66" t="n">
-        <v>201.6899641763442</v>
+        <v>202.1962367582963</v>
       </c>
       <c r="Q66" t="b">
         <v>1</v>
       </c>
       <c r="R66" t="n">
-        <v>-46.25691642417533</v>
+        <v>-42.46049068927504</v>
       </c>
     </row>
     <row r="67">
@@ -4591,25 +4591,25 @@
         <v>130</v>
       </c>
       <c r="L67" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="M67" t="n">
         <v>31.40375764522792</v>
       </c>
       <c r="N67" t="n">
-        <v>89.22066299370901</v>
+        <v>92.49349973125699</v>
       </c>
       <c r="O67" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5588351730509</v>
       </c>
       <c r="P67" t="n">
-        <v>201.6899641763442</v>
+        <v>204.5261674521539</v>
       </c>
       <c r="Q67" t="b">
         <v>1</v>
       </c>
       <c r="R67" t="n">
-        <v>-46.4451284836203</v>
+        <v>-42.51130695393967</v>
       </c>
     </row>
     <row r="68">
@@ -4653,25 +4653,25 @@
         <v>64</v>
       </c>
       <c r="L68" t="n">
-        <v>294.6269652508399</v>
+        <v>292.6089091826404</v>
       </c>
       <c r="M68" t="n">
         <v>14.59172217771132</v>
       </c>
       <c r="N68" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8514915084962</v>
       </c>
       <c r="O68" t="n">
-        <v>82.63013147238911</v>
+        <v>87.79940414161152</v>
       </c>
       <c r="P68" t="n">
-        <v>198.3946984156842</v>
+        <v>202.3254478250539</v>
       </c>
       <c r="Q68" t="b">
         <v>1</v>
       </c>
       <c r="R68" t="n">
-        <v>-48.50546289978281</v>
+        <v>-44.62288967013806</v>
       </c>
     </row>
     <row r="69">
@@ -4684,16 +4684,16 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>49.9963493347168</v>
+        <v>49.99939727783203</v>
       </c>
       <c r="D69" t="n">
-        <v>49.99587631225586</v>
+        <v>50.00261306762695</v>
       </c>
       <c r="E69" t="n">
-        <v>62.39410781860352</v>
+        <v>41.39688491821289</v>
       </c>
       <c r="F69" t="n">
-        <v>9.80394886996327</v>
+        <v>8.092199906374443</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -4712,28 +4712,28 @@
         </is>
       </c>
       <c r="K69" t="n">
-        <v>139</v>
+        <v>63</v>
       </c>
       <c r="L69" t="n">
-        <v>314.1592653589793</v>
+        <v>296.8007748403156</v>
       </c>
       <c r="M69" t="n">
-        <v>35.38608805681638</v>
+        <v>14.3711521043727</v>
       </c>
       <c r="N69" t="n">
-        <v>105.5564219307495</v>
+        <v>316.560670066318</v>
       </c>
       <c r="O69" t="n">
-        <v>314.1592653589793</v>
+        <v>87.79940414161152</v>
       </c>
       <c r="P69" t="n">
-        <v>209.8578436448644</v>
+        <v>202.1800371039648</v>
       </c>
       <c r="Q69" t="b">
         <v>1</v>
       </c>
       <c r="R69" t="n">
-        <v>-49.70098801292402</v>
+        <v>-46.80023759600709</v>
       </c>
     </row>
     <row r="70">
@@ -4746,16 +4746,16 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>49.99333953857422</v>
+        <v>50.00120544433594</v>
       </c>
       <c r="D70" t="n">
-        <v>49.99663925170898</v>
+        <v>49.99996185302734</v>
       </c>
       <c r="E70" t="n">
-        <v>62.46930313110352</v>
+        <v>41.15816116333008</v>
       </c>
       <c r="F70" t="n">
-        <v>9.799032184834553</v>
+        <v>8.231625812104637</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -4774,28 +4774,28 @@
         </is>
       </c>
       <c r="K70" t="n">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="L70" t="n">
-        <v>314.1592653589793</v>
+        <v>300.5870753959373</v>
       </c>
       <c r="M70" t="n">
-        <v>35.46134744806692</v>
+        <v>14.13240678075293</v>
       </c>
       <c r="N70" t="n">
-        <v>105.5564219307495</v>
+        <v>316.5384922424669</v>
       </c>
       <c r="O70" t="n">
-        <v>314.1592653589793</v>
+        <v>87.79940414161152</v>
       </c>
       <c r="P70" t="n">
-        <v>209.8578436448644</v>
+        <v>202.1689481920392</v>
       </c>
       <c r="Q70" t="b">
         <v>1</v>
       </c>
       <c r="R70" t="n">
-        <v>-49.70098801292402</v>
+        <v>-48.68112936434299</v>
       </c>
     </row>
     <row r="71">
@@ -4808,16 +4808,16 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>49.99900436401367</v>
+        <v>49.99333953857422</v>
       </c>
       <c r="D71" t="n">
-        <v>49.99873352050781</v>
+        <v>49.99663925170898</v>
       </c>
       <c r="E71" t="n">
-        <v>62.32781219482422</v>
+        <v>62.46930313110352</v>
       </c>
       <c r="F71" t="n">
-        <v>9.805574255986603</v>
+        <v>9.799032184834553</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -4836,28 +4836,28 @@
         </is>
       </c>
       <c r="K71" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="L71" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="M71" t="n">
-        <v>35.31967779742937</v>
+        <v>35.46134744806692</v>
       </c>
       <c r="N71" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
       <c r="O71" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5195338428691</v>
       </c>
       <c r="P71" t="n">
-        <v>209.8578436448644</v>
+        <v>211.9279141350295</v>
       </c>
       <c r="Q71" t="b">
         <v>1</v>
       </c>
       <c r="R71" t="n">
-        <v>-49.70098801292402</v>
+        <v>-49.75032655790057</v>
       </c>
     </row>
     <row r="72">
@@ -4870,16 +4870,16 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>50.00115203857422</v>
+        <v>50.00551986694336</v>
       </c>
       <c r="D72" t="n">
-        <v>50.00203323364258</v>
+        <v>50.00483703613281</v>
       </c>
       <c r="E72" t="n">
-        <v>62.25125503540039</v>
+        <v>62.12836074829102</v>
       </c>
       <c r="F72" t="n">
-        <v>9.8072623524217</v>
+        <v>9.80995190972968</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -4898,28 +4898,28 @@
         </is>
       </c>
       <c r="K72" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="L72" t="n">
-        <v>314.1592653589793</v>
+        <v>317.5916436821873</v>
       </c>
       <c r="M72" t="n">
-        <v>35.2430194692984</v>
+        <v>35.12001562774382</v>
       </c>
       <c r="N72" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
       <c r="O72" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4973241165592</v>
       </c>
       <c r="P72" t="n">
-        <v>209.8578436448644</v>
+        <v>211.9168092718746</v>
       </c>
       <c r="Q72" t="b">
         <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>-49.70098801292402</v>
+        <v>-49.86618795054587</v>
       </c>
     </row>
     <row r="73">
@@ -4932,16 +4932,16 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>50.00433731079102</v>
+        <v>50.00115203857422</v>
       </c>
       <c r="D73" t="n">
-        <v>50.00821304321289</v>
+        <v>50.00203323364258</v>
       </c>
       <c r="E73" t="n">
-        <v>62.01437377929688</v>
+        <v>62.25125503540039</v>
       </c>
       <c r="F73" t="n">
-        <v>9.807471464757194</v>
+        <v>9.8072623524217</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -4960,28 +4960,28 @@
         </is>
       </c>
       <c r="K73" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="L73" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6134253926882</v>
       </c>
       <c r="M73" t="n">
-        <v>35.00597254394068</v>
+        <v>35.2430194692984</v>
       </c>
       <c r="N73" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
       <c r="O73" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4931987137201</v>
       </c>
       <c r="P73" t="n">
-        <v>209.8578436448644</v>
+        <v>211.914746570455</v>
       </c>
       <c r="Q73" t="b">
         <v>1</v>
       </c>
       <c r="R73" t="n">
-        <v>-49.70098801292402</v>
+        <v>-49.87792521890009</v>
       </c>
     </row>
     <row r="74">
@@ -4994,16 +4994,16 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>50.00551986694336</v>
+        <v>50.00433731079102</v>
       </c>
       <c r="D74" t="n">
-        <v>50.00483703613281</v>
+        <v>50.00821304321289</v>
       </c>
       <c r="E74" t="n">
-        <v>62.12836074829102</v>
+        <v>62.01437377929688</v>
       </c>
       <c r="F74" t="n">
-        <v>9.80995190972968</v>
+        <v>9.807471464757194</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5022,28 +5022,28 @@
         </is>
       </c>
       <c r="K74" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L74" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6236624786501</v>
       </c>
       <c r="M74" t="n">
-        <v>35.12001562774382</v>
+        <v>35.00597254394068</v>
       </c>
       <c r="N74" t="n">
-        <v>105.5564219307495</v>
+        <v>107.33629442719</v>
       </c>
       <c r="O74" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4973241165592</v>
       </c>
       <c r="P74" t="n">
-        <v>209.8578436448644</v>
+        <v>211.9168092718746</v>
       </c>
       <c r="Q74" t="b">
         <v>1</v>
       </c>
       <c r="R74" t="n">
-        <v>-49.70098801292402</v>
+        <v>-49.88129708538646</v>
       </c>
     </row>
     <row r="75">
@@ -5056,16 +5056,16 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>49.99939727783203</v>
+        <v>49.99900436401367</v>
       </c>
       <c r="D75" t="n">
-        <v>50.00261306762695</v>
+        <v>49.99873352050781</v>
       </c>
       <c r="E75" t="n">
-        <v>41.39688491821289</v>
+        <v>62.32781219482422</v>
       </c>
       <c r="F75" t="n">
-        <v>8.092199906374443</v>
+        <v>9.805574255986603</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -5084,28 +5084,28 @@
         </is>
       </c>
       <c r="K75" t="n">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="L75" t="n">
-        <v>299.4512167284911</v>
+        <v>317.6880296600202</v>
       </c>
       <c r="M75" t="n">
-        <v>14.3711521043727</v>
+        <v>35.31967779742937</v>
       </c>
       <c r="N75" t="n">
-        <v>314.1592653589793</v>
+        <v>107.33629442719</v>
       </c>
       <c r="O75" t="n">
-        <v>82.63013147238911</v>
+        <v>316.4931987137201</v>
       </c>
       <c r="P75" t="n">
-        <v>198.3946984156842</v>
+        <v>211.914746570455</v>
       </c>
       <c r="Q75" t="b">
         <v>1</v>
       </c>
       <c r="R75" t="n">
-        <v>-50.93710624316654</v>
+        <v>-49.91313006827438</v>
       </c>
     </row>
     <row r="76">
@@ -5118,16 +5118,16 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>50.00120544433594</v>
+        <v>49.9963493347168</v>
       </c>
       <c r="D76" t="n">
-        <v>49.99996185302734</v>
+        <v>49.99587631225586</v>
       </c>
       <c r="E76" t="n">
-        <v>41.15816116333008</v>
+        <v>62.39410781860352</v>
       </c>
       <c r="F76" t="n">
-        <v>8.231625812104637</v>
+        <v>9.80394886996327</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5146,28 +5146,28 @@
         </is>
       </c>
       <c r="K76" t="n">
-        <v>62</v>
+        <v>139</v>
       </c>
       <c r="L76" t="n">
-        <v>303.9601468164716</v>
+        <v>317.7533179952903</v>
       </c>
       <c r="M76" t="n">
-        <v>14.13240678075293</v>
+        <v>35.38608805681638</v>
       </c>
       <c r="N76" t="n">
-        <v>314.1592653589793</v>
+        <v>107.33629442719</v>
       </c>
       <c r="O76" t="n">
-        <v>82.63013147238911</v>
+        <v>316.4931987137201</v>
       </c>
       <c r="P76" t="n">
-        <v>198.3946984156842</v>
+        <v>211.914746570455</v>
       </c>
       <c r="Q76" t="b">
         <v>1</v>
       </c>
       <c r="R76" t="n">
-        <v>-53.2098131874485</v>
+        <v>-49.94393884223969</v>
       </c>
     </row>
     <row r="77">
@@ -5180,16 +5180,16 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>50.00368499755859</v>
+        <v>49.98567581176758</v>
       </c>
       <c r="D77" t="n">
-        <v>50.00201797485352</v>
+        <v>49.99795150756836</v>
       </c>
       <c r="E77" t="n">
-        <v>37.8358268737793</v>
+        <v>40.91030502319336</v>
       </c>
       <c r="F77" t="n">
-        <v>9.809699818322519</v>
+        <v>8.382297523822627</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5208,28 +5208,28 @@
         </is>
       </c>
       <c r="K77" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="L77" t="n">
-        <v>314.1592653589793</v>
+        <v>304.4916221213158</v>
       </c>
       <c r="M77" t="n">
-        <v>10.80537830364006</v>
+        <v>13.88405646933769</v>
       </c>
       <c r="N77" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5335092876441</v>
       </c>
       <c r="O77" t="n">
-        <v>93.64567667079508</v>
+        <v>86.28379979319364</v>
       </c>
       <c r="P77" t="n">
-        <v>203.9024710148872</v>
+        <v>201.4086545404189</v>
       </c>
       <c r="Q77" t="b">
         <v>1</v>
       </c>
       <c r="R77" t="n">
-        <v>-54.07329974732975</v>
+        <v>-51.18100203594287</v>
       </c>
     </row>
     <row r="78">
@@ -5242,16 +5242,16 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>50.0035514831543</v>
+        <v>49.99497985839844</v>
       </c>
       <c r="D78" t="n">
-        <v>50.00202941894531</v>
+        <v>49.9945068359375</v>
       </c>
       <c r="E78" t="n">
-        <v>37.83469390869141</v>
+        <v>40.62739562988281</v>
       </c>
       <c r="F78" t="n">
-        <v>9.809750625568565</v>
+        <v>8.561291110257489</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5270,28 +5270,28 @@
         </is>
       </c>
       <c r="K78" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="L78" t="n">
-        <v>314.1592653589793</v>
+        <v>308.0233956472299</v>
       </c>
       <c r="M78" t="n">
-        <v>10.80423744126723</v>
+        <v>13.60097316734039</v>
       </c>
       <c r="N78" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8192663418636</v>
       </c>
       <c r="O78" t="n">
-        <v>93.64567667079508</v>
+        <v>86.28379979319364</v>
       </c>
       <c r="P78" t="n">
-        <v>203.9024710148872</v>
+        <v>201.5515330675286</v>
       </c>
       <c r="Q78" t="b">
         <v>1</v>
       </c>
       <c r="R78" t="n">
-        <v>-54.07329974732975</v>
+        <v>-52.82612389955303</v>
       </c>
     </row>
     <row r="79">
@@ -5304,16 +5304,16 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>50.00368881225586</v>
+        <v>50.0035514831543</v>
       </c>
       <c r="D79" t="n">
-        <v>50.00201797485352</v>
+        <v>50.00202941894531</v>
       </c>
       <c r="E79" t="n">
-        <v>37.83584594726562</v>
+        <v>37.83469390869141</v>
       </c>
       <c r="F79" t="n">
-        <v>9.809698992188437</v>
+        <v>9.809750625568565</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5332,28 +5332,28 @@
         </is>
       </c>
       <c r="K79" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L79" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3452100740342</v>
       </c>
       <c r="M79" t="n">
-        <v>10.80539775485585</v>
+        <v>10.80423744126723</v>
       </c>
       <c r="N79" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933721855287</v>
       </c>
       <c r="O79" t="n">
-        <v>93.64567667079508</v>
+        <v>96.35646782615883</v>
       </c>
       <c r="P79" t="n">
-        <v>203.9024710148872</v>
+        <v>206.4249200058438</v>
       </c>
       <c r="Q79" t="b">
         <v>1</v>
       </c>
       <c r="R79" t="n">
-        <v>-54.07329974732975</v>
+        <v>-53.73396296583297</v>
       </c>
     </row>
     <row r="80">
@@ -5366,16 +5366,16 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>49.98567581176758</v>
+        <v>49.98854064941406</v>
       </c>
       <c r="D80" t="n">
-        <v>49.99795150756836</v>
+        <v>49.99430465698242</v>
       </c>
       <c r="E80" t="n">
-        <v>40.91030502319336</v>
+        <v>40.56135177612305</v>
       </c>
       <c r="F80" t="n">
-        <v>8.382297523822627</v>
+        <v>8.603454556285387</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5394,28 +5394,28 @@
         </is>
       </c>
       <c r="K80" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L80" t="n">
-        <v>307.8119344940786</v>
+        <v>308.657563515286</v>
       </c>
       <c r="M80" t="n">
-        <v>13.88405646933769</v>
+        <v>13.53461583987676</v>
       </c>
       <c r="N80" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8192663418636</v>
       </c>
       <c r="O80" t="n">
-        <v>82.09356063317179</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="P80" t="n">
-        <v>198.1264129960755</v>
+        <v>200.0298744108384</v>
       </c>
       <c r="Q80" t="b">
         <v>1</v>
       </c>
       <c r="R80" t="n">
-        <v>-55.36138258364151</v>
+        <v>-54.30573279336204</v>
       </c>
     </row>
     <row r="81">
@@ -5428,16 +5428,16 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>49.98917770385742</v>
+        <v>49.98777389526367</v>
       </c>
       <c r="D81" t="n">
-        <v>49.99966430664062</v>
+        <v>49.9942512512207</v>
       </c>
       <c r="E81" t="n">
-        <v>38.70668411254883</v>
+        <v>40.26611328125</v>
       </c>
       <c r="F81" t="n">
-        <v>9.741179232728644</v>
+        <v>8.794277311280105</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5456,28 +5456,28 @@
         </is>
       </c>
       <c r="K81" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L81" t="n">
-        <v>314.1592653589793</v>
+        <v>311.512646269697</v>
       </c>
       <c r="M81" t="n">
-        <v>11.67655592325729</v>
+        <v>13.23937486094671</v>
       </c>
       <c r="N81" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041631445446</v>
       </c>
       <c r="O81" t="n">
-        <v>86.40674033045698</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="P81" t="n">
-        <v>200.2830028447182</v>
+        <v>199.8723228121789</v>
       </c>
       <c r="Q81" t="b">
         <v>1</v>
       </c>
       <c r="R81" t="n">
-        <v>-56.85767683568774</v>
+        <v>-55.85581929841636</v>
       </c>
     </row>
     <row r="82">
@@ -5490,16 +5490,16 @@
         </is>
       </c>
       <c r="C82" t="n">
-        <v>49.99501037597656</v>
+        <v>49.98774719238281</v>
       </c>
       <c r="D82" t="n">
-        <v>49.99667358398438</v>
+        <v>49.9942512512207</v>
       </c>
       <c r="E82" t="n">
-        <v>38.50731658935547</v>
+        <v>40.26636505126953</v>
       </c>
       <c r="F82" t="n">
-        <v>9.820611923690013</v>
+        <v>8.794112156754611</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5518,28 +5518,28 @@
         </is>
       </c>
       <c r="K82" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="L82" t="n">
-        <v>314.1592653589793</v>
+        <v>311.8112845122635</v>
       </c>
       <c r="M82" t="n">
-        <v>11.47694574343044</v>
+        <v>13.23962804306808</v>
       </c>
       <c r="N82" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041631445446</v>
       </c>
       <c r="O82" t="n">
-        <v>86.40674033045698</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="P82" t="n">
-        <v>200.2830028447182</v>
+        <v>199.8723228121789</v>
       </c>
       <c r="Q82" t="b">
         <v>1</v>
       </c>
       <c r="R82" t="n">
-        <v>-56.85767683568774</v>
+        <v>-56.00523380381895</v>
       </c>
     </row>
     <row r="83">
@@ -5552,16 +5552,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>49.99659729003906</v>
+        <v>49.99403381347656</v>
       </c>
       <c r="D83" t="n">
-        <v>49.99772644042969</v>
+        <v>49.99443054199219</v>
       </c>
       <c r="E83" t="n">
-        <v>38.56888580322266</v>
+        <v>40.20368957519531</v>
       </c>
       <c r="F83" t="n">
-        <v>9.820571691415743</v>
+        <v>8.835400788128018</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5580,28 +5580,28 @@
         </is>
       </c>
       <c r="K83" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L83" t="n">
-        <v>314.1592653589793</v>
+        <v>312.0935691643398</v>
       </c>
       <c r="M83" t="n">
-        <v>11.53854440331165</v>
+        <v>13.17663780810857</v>
       </c>
       <c r="N83" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041631445446</v>
       </c>
       <c r="O83" t="n">
-        <v>86.40674033045698</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="P83" t="n">
-        <v>200.2830028447182</v>
+        <v>199.8723228121789</v>
       </c>
       <c r="Q83" t="b">
         <v>1</v>
       </c>
       <c r="R83" t="n">
-        <v>-56.85767683568774</v>
+        <v>-56.14646629069091</v>
       </c>
     </row>
     <row r="84">
@@ -5614,16 +5614,16 @@
         </is>
       </c>
       <c r="C84" t="n">
-        <v>49.99497985839844</v>
+        <v>49.99501037597656</v>
       </c>
       <c r="D84" t="n">
-        <v>49.9945068359375</v>
+        <v>49.99667358398438</v>
       </c>
       <c r="E84" t="n">
-        <v>40.62739562988281</v>
+        <v>38.50731658935547</v>
       </c>
       <c r="F84" t="n">
-        <v>8.561291110257489</v>
+        <v>9.820611923690013</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5642,28 +5642,28 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="L84" t="n">
-        <v>311.1252778901723</v>
+        <v>317.765308243337</v>
       </c>
       <c r="M84" t="n">
-        <v>13.60097316734039</v>
+        <v>11.47694574343044</v>
       </c>
       <c r="N84" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938489206801</v>
       </c>
       <c r="O84" t="n">
-        <v>82.09356063317179</v>
+        <v>90.17524071230476</v>
       </c>
       <c r="P84" t="n">
-        <v>198.1264129960755</v>
+        <v>203.3345448164924</v>
       </c>
       <c r="Q84" t="b">
         <v>1</v>
       </c>
       <c r="R84" t="n">
-        <v>-57.03372063589271</v>
+        <v>-56.27708933084503</v>
       </c>
     </row>
     <row r="85">
@@ -5676,16 +5676,16 @@
         </is>
       </c>
       <c r="C85" t="n">
-        <v>49.99487686157227</v>
+        <v>50.00368881225586</v>
       </c>
       <c r="D85" t="n">
-        <v>49.98703384399414</v>
+        <v>50.00201797485352</v>
       </c>
       <c r="E85" t="n">
-        <v>38.83555603027344</v>
+        <v>37.83584594726562</v>
       </c>
       <c r="F85" t="n">
-        <v>9.667698113453547</v>
+        <v>9.809698992188437</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -5704,28 +5704,28 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L85" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839805802706</v>
       </c>
       <c r="M85" t="n">
-        <v>11.80617066070385</v>
+        <v>10.80539775485585</v>
       </c>
       <c r="N85" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933721855287</v>
       </c>
       <c r="O85" t="n">
-        <v>82.71263007328757</v>
+        <v>96.35646782615883</v>
       </c>
       <c r="P85" t="n">
-        <v>198.4359477161335</v>
+        <v>206.4249200058438</v>
       </c>
       <c r="Q85" t="b">
         <v>1</v>
       </c>
       <c r="R85" t="n">
-        <v>-58.31771862646096</v>
+        <v>-56.36870808579349</v>
       </c>
     </row>
     <row r="86">
@@ -5738,16 +5738,16 @@
         </is>
       </c>
       <c r="C86" t="n">
-        <v>49.98751831054688</v>
+        <v>50.00368499755859</v>
       </c>
       <c r="D86" t="n">
-        <v>50.00981521606445</v>
+        <v>50.00201797485352</v>
       </c>
       <c r="E86" t="n">
-        <v>61.42176818847656</v>
+        <v>37.8358268737793</v>
       </c>
       <c r="F86" t="n">
-        <v>9.811674038537797</v>
+        <v>9.809699818322519</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5766,28 +5766,28 @@
         </is>
       </c>
       <c r="K86" t="n">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="L86" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839979743623</v>
       </c>
       <c r="M86" t="n">
-        <v>34.41312616249051</v>
+        <v>10.80537830364006</v>
       </c>
       <c r="N86" t="n">
-        <v>82.63013147238911</v>
+        <v>316.4933721855287</v>
       </c>
       <c r="O86" t="n">
-        <v>314.1592653589793</v>
+        <v>96.35646782615883</v>
       </c>
       <c r="P86" t="n">
-        <v>198.3946984156842</v>
+        <v>206.4249200058438</v>
       </c>
       <c r="Q86" t="b">
         <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>-58.35063530817781</v>
+        <v>-56.36871651214614</v>
       </c>
     </row>
     <row r="87">
@@ -5800,16 +5800,16 @@
         </is>
       </c>
       <c r="C87" t="n">
-        <v>49.98854064941406</v>
+        <v>49.98917770385742</v>
       </c>
       <c r="D87" t="n">
-        <v>49.99430465698242</v>
+        <v>49.99966430664062</v>
       </c>
       <c r="E87" t="n">
-        <v>40.56135177612305</v>
+        <v>38.70668411254883</v>
       </c>
       <c r="F87" t="n">
-        <v>8.603454556285387</v>
+        <v>9.741179232728644</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5828,28 +5828,28 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L87" t="n">
-        <v>311.7276708407379</v>
+        <v>318.0311875471213</v>
       </c>
       <c r="M87" t="n">
-        <v>13.53461583987676</v>
+        <v>11.67655592325729</v>
       </c>
       <c r="N87" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5118241388803</v>
       </c>
       <c r="O87" t="n">
-        <v>78.69586983587868</v>
+        <v>90.17524071230476</v>
       </c>
       <c r="P87" t="n">
-        <v>196.427567597429</v>
+        <v>203.3435324255925</v>
       </c>
       <c r="Q87" t="b">
         <v>1</v>
       </c>
       <c r="R87" t="n">
-        <v>-58.69853435217005</v>
+        <v>-56.40093577281355</v>
       </c>
     </row>
     <row r="88">
@@ -5862,16 +5862,16 @@
         </is>
       </c>
       <c r="C88" t="n">
-        <v>50.0224609375</v>
+        <v>49.99659729003906</v>
       </c>
       <c r="D88" t="n">
-        <v>49.98954010009766</v>
+        <v>49.99772644042969</v>
       </c>
       <c r="E88" t="n">
-        <v>39.5126953125</v>
+        <v>38.56888580322266</v>
       </c>
       <c r="F88" t="n">
-        <v>9.266077772580323</v>
+        <v>9.820571691415743</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -5890,28 +5890,28 @@
         </is>
       </c>
       <c r="K88" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L88" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0898230931229</v>
       </c>
       <c r="M88" t="n">
-        <v>12.48456907519561</v>
+        <v>11.53854440331165</v>
       </c>
       <c r="N88" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5118241388803</v>
       </c>
       <c r="O88" t="n">
-        <v>80.890045133328</v>
+        <v>90.17524071230476</v>
       </c>
       <c r="P88" t="n">
-        <v>197.5246552461537</v>
+        <v>203.3435324255925</v>
       </c>
       <c r="Q88" t="b">
         <v>1</v>
       </c>
       <c r="R88" t="n">
-        <v>-59.04812741856278</v>
+        <v>-56.42977148020103</v>
       </c>
     </row>
     <row r="89">
@@ -5924,16 +5924,16 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>50.0231819152832</v>
+        <v>49.99813079833984</v>
       </c>
       <c r="D89" t="n">
-        <v>49.97821044921875</v>
+        <v>49.99911117553711</v>
       </c>
       <c r="E89" t="n">
-        <v>39.28559494018555</v>
+        <v>40.05978012084961</v>
       </c>
       <c r="F89" t="n">
-        <v>9.396393875463914</v>
+        <v>8.927762094352545</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -5952,28 +5952,28 @@
         </is>
       </c>
       <c r="K89" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="L89" t="n">
-        <v>314.1592653589793</v>
+        <v>313.3667832967068</v>
       </c>
       <c r="M89" t="n">
-        <v>12.25718512698606</v>
+        <v>13.03259397913479</v>
       </c>
       <c r="N89" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041631445446</v>
       </c>
       <c r="O89" t="n">
-        <v>80.890045133328</v>
+        <v>82.64878673439914</v>
       </c>
       <c r="P89" t="n">
-        <v>197.5246552461537</v>
+        <v>199.5764749394719</v>
       </c>
       <c r="Q89" t="b">
         <v>1</v>
       </c>
       <c r="R89" t="n">
-        <v>-59.04812741856278</v>
+        <v>-57.01589247517551</v>
       </c>
     </row>
     <row r="90">
@@ -5986,16 +5986,16 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>50.02048873901367</v>
+        <v>49.98417282104492</v>
       </c>
       <c r="D90" t="n">
-        <v>49.99282836914062</v>
+        <v>50.01771545410156</v>
       </c>
       <c r="E90" t="n">
-        <v>39.53869247436523</v>
+        <v>60.00893402099609</v>
       </c>
       <c r="F90" t="n">
-        <v>9.251479081997509</v>
+        <v>8.96396090221393</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -6014,28 +6014,28 @@
         </is>
       </c>
       <c r="K90" t="n">
-        <v>51</v>
+        <v>131</v>
       </c>
       <c r="L90" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="M90" t="n">
-        <v>12.51084748278083</v>
+        <v>32.99812123673607</v>
       </c>
       <c r="N90" t="n">
-        <v>314.1592653589793</v>
+        <v>82.64878673439914</v>
       </c>
       <c r="O90" t="n">
-        <v>80.890045133328</v>
+        <v>316.5095522228258</v>
       </c>
       <c r="P90" t="n">
-        <v>197.5246552461537</v>
+        <v>199.5791694786125</v>
       </c>
       <c r="Q90" t="b">
         <v>1</v>
       </c>
       <c r="R90" t="n">
-        <v>-59.04812741856278</v>
+        <v>-57.20019571666582</v>
       </c>
     </row>
     <row r="91">
@@ -6048,16 +6048,16 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>49.98774719238281</v>
+        <v>49.98751831054688</v>
       </c>
       <c r="D91" t="n">
-        <v>49.9942512512207</v>
+        <v>50.00981521606445</v>
       </c>
       <c r="E91" t="n">
-        <v>40.26636505126953</v>
+        <v>61.42176818847656</v>
       </c>
       <c r="F91" t="n">
-        <v>8.794112156754611</v>
+        <v>9.811674038537797</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -6076,28 +6076,28 @@
         </is>
       </c>
       <c r="K91" t="n">
-        <v>58</v>
+        <v>134</v>
       </c>
       <c r="L91" t="n">
-        <v>313.609850167252</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="M91" t="n">
-        <v>13.23962804306808</v>
+        <v>34.41312616249051</v>
       </c>
       <c r="N91" t="n">
-        <v>314.1592653589793</v>
+        <v>87.79940414161152</v>
       </c>
       <c r="O91" t="n">
-        <v>78.69586983587868</v>
+        <v>316.4938068880664</v>
       </c>
       <c r="P91" t="n">
-        <v>196.427567597429</v>
+        <v>202.1466055148389</v>
       </c>
       <c r="Q91" t="b">
         <v>1</v>
       </c>
       <c r="R91" t="n">
-        <v>-59.65673963340201</v>
+        <v>-57.23865835652366</v>
       </c>
     </row>
     <row r="92">
@@ -6110,16 +6110,16 @@
         </is>
       </c>
       <c r="C92" t="n">
-        <v>49.98777389526367</v>
+        <v>50.0224609375</v>
       </c>
       <c r="D92" t="n">
-        <v>49.9942512512207</v>
+        <v>49.98954010009766</v>
       </c>
       <c r="E92" t="n">
-        <v>40.26611328125</v>
+        <v>39.5126953125</v>
       </c>
       <c r="F92" t="n">
-        <v>8.794277311280105</v>
+        <v>9.266077772580323</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -6138,28 +6138,28 @@
         </is>
       </c>
       <c r="K92" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="L92" t="n">
-        <v>313.6108872403111</v>
+        <v>316.5411432908892</v>
       </c>
       <c r="M92" t="n">
-        <v>13.23937486094671</v>
+        <v>12.48456907519561</v>
       </c>
       <c r="N92" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8977388744225</v>
       </c>
       <c r="O92" t="n">
-        <v>78.69586983587868</v>
+        <v>84.82789715314635</v>
       </c>
       <c r="P92" t="n">
-        <v>196.427567597429</v>
+        <v>200.8628180137844</v>
       </c>
       <c r="Q92" t="b">
         <v>1</v>
       </c>
       <c r="R92" t="n">
-        <v>-59.6572676005666</v>
+        <v>-57.59071112363176</v>
       </c>
     </row>
     <row r="93">
@@ -6172,16 +6172,16 @@
         </is>
       </c>
       <c r="C93" t="n">
-        <v>49.99403381347656</v>
+        <v>50.02048873901367</v>
       </c>
       <c r="D93" t="n">
-        <v>49.99443054199219</v>
+        <v>49.99282836914062</v>
       </c>
       <c r="E93" t="n">
-        <v>40.20368957519531</v>
+        <v>39.53869247436523</v>
       </c>
       <c r="F93" t="n">
-        <v>8.835400788128018</v>
+        <v>9.251479081997509</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -6200,28 +6200,28 @@
         </is>
       </c>
       <c r="K93" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L93" t="n">
-        <v>313.8378490533948</v>
+        <v>316.4174930269139</v>
       </c>
       <c r="M93" t="n">
-        <v>13.17663780810857</v>
+        <v>12.51084748278083</v>
       </c>
       <c r="N93" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4982004585777</v>
       </c>
       <c r="O93" t="n">
-        <v>78.69586983587868</v>
+        <v>84.82789715314635</v>
       </c>
       <c r="P93" t="n">
-        <v>196.427567597429</v>
+        <v>200.663048805862</v>
       </c>
       <c r="Q93" t="b">
         <v>1</v>
       </c>
       <c r="R93" t="n">
-        <v>-59.77281238679992</v>
+        <v>-57.68597901302807</v>
       </c>
     </row>
     <row r="94">
@@ -6234,16 +6234,16 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>49.98993301391602</v>
+        <v>50.00614547729492</v>
       </c>
       <c r="D94" t="n">
-        <v>50.0003776550293</v>
+        <v>49.9990348815918</v>
       </c>
       <c r="E94" t="n">
-        <v>60.30797576904297</v>
+        <v>39.8743896484375</v>
       </c>
       <c r="F94" t="n">
-        <v>9.157319257633926</v>
+        <v>9.046872819089765</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -6262,28 +6262,28 @@
         </is>
       </c>
       <c r="K94" t="n">
-        <v>132</v>
+        <v>54</v>
       </c>
       <c r="L94" t="n">
-        <v>314.1592653589793</v>
+        <v>314.8568266646905</v>
       </c>
       <c r="M94" t="n">
-        <v>33.29772054610363</v>
+        <v>12.84703032924423</v>
       </c>
       <c r="N94" t="n">
-        <v>78.69586983587868</v>
+        <v>316.5041631445446</v>
       </c>
       <c r="O94" t="n">
-        <v>314.1592653589793</v>
+        <v>82.64878673439914</v>
       </c>
       <c r="P94" t="n">
-        <v>196.427567597429</v>
+        <v>199.5764749394719</v>
       </c>
       <c r="Q94" t="b">
         <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>-59.93644334222834</v>
+        <v>-57.76249518395451</v>
       </c>
     </row>
     <row r="95">
@@ -6296,16 +6296,16 @@
         </is>
       </c>
       <c r="C95" t="n">
-        <v>49.97929382324219</v>
+        <v>49.98993301391602</v>
       </c>
       <c r="D95" t="n">
-        <v>49.98659515380859</v>
+        <v>50.0003776550293</v>
       </c>
       <c r="E95" t="n">
-        <v>60.42307662963867</v>
+        <v>60.30797576904297</v>
       </c>
       <c r="F95" t="n">
-        <v>9.22331386674108</v>
+        <v>9.157319257633926</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -6324,28 +6324,28 @@
         </is>
       </c>
       <c r="K95" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L95" t="n">
-        <v>314.1592653589793</v>
+        <v>315.6279461454779</v>
       </c>
       <c r="M95" t="n">
-        <v>33.41413084559626</v>
+        <v>33.29772054610363</v>
       </c>
       <c r="N95" t="n">
-        <v>78.69586983587868</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="O95" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977360874286</v>
       </c>
       <c r="P95" t="n">
-        <v>196.427567597429</v>
+        <v>199.8691092836209</v>
       </c>
       <c r="Q95" t="b">
         <v>1</v>
       </c>
       <c r="R95" t="n">
-        <v>-59.93644334222834</v>
+        <v>-57.91732263017764</v>
       </c>
     </row>
     <row r="96">
@@ -6358,16 +6358,16 @@
         </is>
       </c>
       <c r="C96" t="n">
-        <v>49.99813079833984</v>
+        <v>50.00678253173828</v>
       </c>
       <c r="D96" t="n">
-        <v>49.99911117553711</v>
+        <v>49.99886322021484</v>
       </c>
       <c r="E96" t="n">
-        <v>40.05978012084961</v>
+        <v>39.77205657958984</v>
       </c>
       <c r="F96" t="n">
-        <v>8.927762094352545</v>
+        <v>9.111345828770014</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -6386,28 +6386,28 @@
         </is>
       </c>
       <c r="K96" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L96" t="n">
-        <v>314.1315652890347</v>
+        <v>315.186469065413</v>
       </c>
       <c r="M96" t="n">
-        <v>13.03259397913479</v>
+        <v>12.744691629923</v>
       </c>
       <c r="N96" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4982004585777</v>
       </c>
       <c r="O96" t="n">
-        <v>78.5399454490972</v>
+        <v>82.64878673439914</v>
       </c>
       <c r="P96" t="n">
-        <v>196.3496054040383</v>
+        <v>199.5734935964884</v>
       </c>
       <c r="Q96" t="b">
         <v>1</v>
       </c>
       <c r="R96" t="n">
-        <v>-59.98583987099471</v>
+        <v>-57.9300253683382</v>
       </c>
     </row>
     <row r="97">
@@ -6451,25 +6451,25 @@
         <v>53</v>
       </c>
       <c r="L97" t="n">
-        <v>314.1592653589793</v>
+        <v>315.3488601235974</v>
       </c>
       <c r="M97" t="n">
         <v>12.74901423574446</v>
       </c>
       <c r="N97" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4982004585777</v>
       </c>
       <c r="O97" t="n">
-        <v>78.5399454490972</v>
+        <v>82.64878673439914</v>
       </c>
       <c r="P97" t="n">
-        <v>196.3496054040383</v>
+        <v>199.5734935964884</v>
       </c>
       <c r="Q97" t="b">
         <v>1</v>
       </c>
       <c r="R97" t="n">
-        <v>-59.99994739613472</v>
+        <v>-58.01139441953731</v>
       </c>
     </row>
     <row r="98">
@@ -6482,16 +6482,16 @@
         </is>
       </c>
       <c r="C98" t="n">
-        <v>50.00678253173828</v>
+        <v>49.99487686157227</v>
       </c>
       <c r="D98" t="n">
-        <v>49.99886322021484</v>
+        <v>49.98703384399414</v>
       </c>
       <c r="E98" t="n">
-        <v>39.77205657958984</v>
+        <v>38.83555603027344</v>
       </c>
       <c r="F98" t="n">
-        <v>9.111345828770014</v>
+        <v>9.667698113453547</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -6510,28 +6510,28 @@
         </is>
       </c>
       <c r="K98" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="L98" t="n">
-        <v>314.1592653589793</v>
+        <v>318.6565806888216</v>
       </c>
       <c r="M98" t="n">
-        <v>12.744691629923</v>
+        <v>11.80617066070385</v>
       </c>
       <c r="N98" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951254556041</v>
       </c>
       <c r="O98" t="n">
-        <v>78.5399454490972</v>
+        <v>86.76001954747389</v>
       </c>
       <c r="P98" t="n">
-        <v>196.3496054040383</v>
+        <v>201.627572501539</v>
       </c>
       <c r="Q98" t="b">
         <v>1</v>
       </c>
       <c r="R98" t="n">
-        <v>-59.99994739613472</v>
+        <v>-58.04216493574526</v>
       </c>
     </row>
     <row r="99">
@@ -6544,16 +6544,16 @@
         </is>
       </c>
       <c r="C99" t="n">
-        <v>50.00614547729492</v>
+        <v>50.0231819152832</v>
       </c>
       <c r="D99" t="n">
-        <v>49.9990348815918</v>
+        <v>49.97821044921875</v>
       </c>
       <c r="E99" t="n">
-        <v>39.8743896484375</v>
+        <v>39.28559494018555</v>
       </c>
       <c r="F99" t="n">
-        <v>9.046872819089765</v>
+        <v>9.396393875463914</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -6572,28 +6572,28 @@
         </is>
       </c>
       <c r="K99" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L99" t="n">
-        <v>314.1592653589793</v>
+        <v>317.2623272318006</v>
       </c>
       <c r="M99" t="n">
-        <v>12.84703032924423</v>
+        <v>12.25718512698606</v>
       </c>
       <c r="N99" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977227416219</v>
       </c>
       <c r="O99" t="n">
-        <v>78.5399454490972</v>
+        <v>84.82789715314635</v>
       </c>
       <c r="P99" t="n">
-        <v>196.3496054040383</v>
+        <v>200.6628099473841</v>
       </c>
       <c r="Q99" t="b">
         <v>1</v>
       </c>
       <c r="R99" t="n">
-        <v>-59.99994739613472</v>
+        <v>-58.10718852934931</v>
       </c>
     </row>
     <row r="100">
@@ -6606,16 +6606,16 @@
         </is>
       </c>
       <c r="C100" t="n">
-        <v>49.98417282104492</v>
+        <v>49.97929382324219</v>
       </c>
       <c r="D100" t="n">
-        <v>50.01771545410156</v>
+        <v>49.98659515380859</v>
       </c>
       <c r="E100" t="n">
-        <v>60.00893402099609</v>
+        <v>60.42307662963867</v>
       </c>
       <c r="F100" t="n">
-        <v>8.96396090221393</v>
+        <v>9.22331386674108</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -6634,28 +6634,28 @@
         </is>
       </c>
       <c r="K100" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.1547027829528</v>
       </c>
       <c r="M100" t="n">
-        <v>32.99812123673607</v>
+        <v>33.41413084559626</v>
       </c>
       <c r="N100" t="n">
-        <v>78.5399454490972</v>
+        <v>83.24048247981317</v>
       </c>
       <c r="O100" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977360874286</v>
       </c>
       <c r="P100" t="n">
-        <v>196.3496054040383</v>
+        <v>199.8691092836209</v>
       </c>
       <c r="Q100" t="b">
         <v>1</v>
       </c>
       <c r="R100" t="n">
-        <v>-59.99994739613472</v>
+        <v>-58.1808734306805</v>
       </c>
     </row>
     <row r="101">
@@ -6699,14 +6699,14 @@
         <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956798713022</v>
       </c>
       <c r="M101" t="n">
         <v>0</v>
       </c>
       <c r="N101" t="inlineStr"/>
       <c r="O101" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="P101" t="inlineStr"/>
       <c r="Q101" t="b">
@@ -6755,14 +6755,14 @@
         <v>1</v>
       </c>
       <c r="L102" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956864249835</v>
       </c>
       <c r="M102" t="n">
         <v>0.001928344560479429</v>
       </c>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="P102" t="inlineStr"/>
       <c r="Q102" t="b">
@@ -6811,14 +6811,14 @@
         <v>2</v>
       </c>
       <c r="L103" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4972710745226</v>
       </c>
       <c r="M103" t="n">
         <v>0.004646351162764988</v>
       </c>
       <c r="N103" t="inlineStr"/>
       <c r="O103" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="P103" t="inlineStr"/>
       <c r="Q103" t="b">
@@ -6867,14 +6867,14 @@
         <v>3</v>
       </c>
       <c r="L104" t="n">
-        <v>314.1592653589793</v>
+        <v>333.624825899545</v>
       </c>
       <c r="M104" t="n">
         <v>0.4873372702027673</v>
       </c>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3452100740342</v>
       </c>
       <c r="P104" t="inlineStr"/>
       <c r="Q104" t="b">
@@ -6923,14 +6923,14 @@
         <v>4</v>
       </c>
       <c r="L105" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5201844920101</v>
       </c>
       <c r="M105" t="n">
         <v>0.4873493333347039</v>
       </c>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3452100740342</v>
       </c>
       <c r="P105" t="inlineStr"/>
       <c r="Q105" t="b">
@@ -6979,14 +6979,14 @@
         <v>5</v>
       </c>
       <c r="L106" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5201759106017</v>
       </c>
       <c r="M106" t="n">
         <v>0.5074754882102908</v>
       </c>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3452100740342</v>
       </c>
       <c r="P106" t="inlineStr"/>
       <c r="Q106" t="b">
@@ -7035,14 +7035,14 @@
         <v>6</v>
       </c>
       <c r="L107" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933721855287</v>
       </c>
       <c r="M107" t="n">
         <v>0.99446371398485</v>
       </c>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839805802706</v>
       </c>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="b">
@@ -7091,14 +7091,14 @@
         <v>7</v>
       </c>
       <c r="L108" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938953908455</v>
       </c>
       <c r="M108" t="n">
         <v>0.9963882325360288</v>
       </c>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839805802706</v>
       </c>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="b">
@@ -7147,14 +7147,14 @@
         <v>8</v>
       </c>
       <c r="L109" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4942734305535</v>
       </c>
       <c r="M109" t="n">
         <v>1.003184137127545</v>
       </c>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="n">
-        <v>314.1592653589793</v>
+        <v>322.7839805802706</v>
       </c>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="b">
@@ -7203,14 +7203,14 @@
         <v>9</v>
       </c>
       <c r="L110" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938489206801</v>
       </c>
       <c r="M110" t="n">
         <v>1.481875346985952</v>
       </c>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="b">
@@ -7259,14 +7259,14 @@
         <v>10</v>
       </c>
       <c r="L111" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5117826027279</v>
       </c>
       <c r="M111" t="n">
         <v>1.48190887511521</v>
       </c>
       <c r="N111" t="inlineStr"/>
       <c r="O111" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="b">
@@ -7315,14 +7315,14 @@
         <v>11</v>
       </c>
       <c r="L112" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5118241388803</v>
       </c>
       <c r="M112" t="n">
         <v>1.505954279737163</v>
       </c>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="n">
-        <v>314.1592653589793</v>
+        <v>317.765308243337</v>
       </c>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="b">
@@ -7371,14 +7371,14 @@
         <v>12</v>
       </c>
       <c r="L113" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951254556041</v>
       </c>
       <c r="M113" t="n">
         <v>1.994928049811479</v>
       </c>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="n">
-        <v>314.1592653589793</v>
+        <v>318.6565806888216</v>
       </c>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="b">
@@ -7427,14 +7427,14 @@
         <v>13</v>
       </c>
       <c r="L114" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4960806526422</v>
       </c>
       <c r="M114" t="n">
         <v>1.997022325558746</v>
       </c>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="n">
-        <v>314.1592653589793</v>
+        <v>318.6565806888216</v>
       </c>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="b">
@@ -7483,14 +7483,14 @@
         <v>14</v>
       </c>
       <c r="L115" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4996263630704</v>
       </c>
       <c r="M115" t="n">
         <v>2.002752083392839</v>
       </c>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="n">
-        <v>314.1592653589793</v>
+        <v>318.6565806888216</v>
       </c>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="b">
@@ -7539,14 +7539,14 @@
         <v>15</v>
       </c>
       <c r="L116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977227416219</v>
       </c>
       <c r="M116" t="n">
         <v>2.449115629575422</v>
       </c>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5411432908892</v>
       </c>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="b">
@@ -7595,14 +7595,14 @@
         <v>16</v>
       </c>
       <c r="L117" t="n">
-        <v>314.1592653589793</v>
+        <v>319.119833396043</v>
       </c>
       <c r="M117" t="n">
         <v>2.449238708995931</v>
       </c>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5411432908892</v>
       </c>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="b">
@@ -7651,14 +7651,14 @@
         <v>17</v>
       </c>
       <c r="L118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8977388744225</v>
       </c>
       <c r="M118" t="n">
         <v>2.504506381320375</v>
       </c>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4174930269139</v>
       </c>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="b">
@@ -7707,14 +7707,14 @@
         <v>18</v>
       </c>
       <c r="L119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4982004585777</v>
       </c>
       <c r="M119" t="n">
         <v>2.505325664714451</v>
       </c>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4174930269139</v>
       </c>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="b">
@@ -7763,14 +7763,14 @@
         <v>19</v>
       </c>
       <c r="L120" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5041631445446</v>
       </c>
       <c r="M120" t="n">
         <v>3.005896073775991</v>
       </c>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="n">
-        <v>314.1315652890347</v>
+        <v>313.3667832967068</v>
       </c>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="b">
@@ -7819,14 +7819,14 @@
         <v>20</v>
       </c>
       <c r="L121" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8191053532236</v>
       </c>
       <c r="M121" t="n">
         <v>3.500336232004733</v>
       </c>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="n">
-        <v>311.7276708407379</v>
+        <v>308.657563515286</v>
       </c>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="b">
@@ -7875,14 +7875,14 @@
         <v>21</v>
       </c>
       <c r="L122" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8192663418636</v>
       </c>
       <c r="M122" t="n">
         <v>3.505765901160193</v>
       </c>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="n">
-        <v>311.7276708407379</v>
+        <v>308.657563515286</v>
       </c>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="b">
@@ -7931,14 +7931,14 @@
         <v>22</v>
       </c>
       <c r="L123" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5335092876441</v>
       </c>
       <c r="M123" t="n">
         <v>3.99522030550304</v>
       </c>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="n">
-        <v>307.8119344940786</v>
+        <v>304.4916221213158</v>
       </c>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="b">
@@ -7987,14 +7987,14 @@
         <v>23</v>
       </c>
       <c r="L124" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5384922424669</v>
       </c>
       <c r="M124" t="n">
         <v>4.006576816231968</v>
       </c>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="n">
-        <v>307.8119344940786</v>
+        <v>304.4916221213158</v>
       </c>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="b">
@@ -8043,14 +8043,14 @@
         <v>24</v>
       </c>
       <c r="L125" t="n">
-        <v>314.1592653589793</v>
+        <v>316.560670066318</v>
       </c>
       <c r="M125" t="n">
         <v>4.50219760087815</v>
       </c>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="n">
-        <v>294.6269652508399</v>
+        <v>292.6089091826404</v>
       </c>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="b">
@@ -8099,14 +8099,14 @@
         <v>25</v>
       </c>
       <c r="L126" t="n">
-        <v>314.1592653589793</v>
+        <v>316.8514915084962</v>
       </c>
       <c r="M126" t="n">
         <v>4.5093929372737</v>
       </c>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="n">
-        <v>294.6269652508399</v>
+        <v>292.6089091826404</v>
       </c>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="b">
@@ -8155,14 +8155,14 @@
         <v>26</v>
       </c>
       <c r="L127" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5930693749811</v>
       </c>
       <c r="M127" t="n">
         <v>5.000352219119195</v>
       </c>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="n">
-        <v>286.2196126656559</v>
+        <v>285.0381023203544</v>
       </c>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="b">
@@ -8211,14 +8211,14 @@
         <v>27</v>
       </c>
       <c r="L128" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6223582354581</v>
       </c>
       <c r="M128" t="n">
         <v>5.510687044421509</v>
       </c>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="b">
@@ -8267,14 +8267,14 @@
         <v>28</v>
       </c>
       <c r="L129" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6357038559812</v>
       </c>
       <c r="M129" t="n">
         <v>5.962606754083162</v>
       </c>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="b">
@@ -8323,14 +8323,14 @@
         <v>29</v>
       </c>
       <c r="L130" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6418857289111</v>
       </c>
       <c r="M130" t="n">
         <v>5.965544132903944</v>
       </c>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="n">
-        <v>253.4092476203645</v>
+        <v>254.9553963130502</v>
       </c>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="b">
@@ -8379,14 +8379,14 @@
         <v>30</v>
       </c>
       <c r="L131" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6143668288898</v>
       </c>
       <c r="M131" t="n">
         <v>6.499869347686423</v>
       </c>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="n">
-        <v>234.6376077615358</v>
+        <v>236.6410918994229</v>
       </c>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="b">
@@ -8435,14 +8435,14 @@
         <v>31</v>
       </c>
       <c r="L132" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5626661416117</v>
       </c>
       <c r="M132" t="n">
         <v>6.930896066808852</v>
       </c>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="n">
-        <v>213.719050856379</v>
+        <v>215.8886209778705</v>
       </c>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="b">
@@ -8491,14 +8491,14 @@
         <v>32</v>
       </c>
       <c r="L133" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5778275061289</v>
       </c>
       <c r="M133" t="n">
         <v>6.944320704636442</v>
       </c>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="n">
-        <v>213.719050856379</v>
+        <v>215.8886209778705</v>
       </c>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="b">
@@ -8547,14 +8547,14 @@
         <v>33</v>
       </c>
       <c r="L134" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4519340162132</v>
       </c>
       <c r="M134" t="n">
         <v>7.459816376211158</v>
       </c>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="n">
-        <v>197.5050285414572</v>
+        <v>199.53895674502</v>
       </c>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="b">
@@ -8603,14 +8603,14 @@
         <v>34</v>
       </c>
       <c r="L135" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3463324831218</v>
       </c>
       <c r="M135" t="n">
         <v>7.872730740862041</v>
       </c>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="n">
-        <v>180.5367905217445</v>
+        <v>183.2890629174703</v>
       </c>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="b">
@@ -8659,14 +8659,14 @@
         <v>35</v>
       </c>
       <c r="L136" t="n">
-        <v>314.1592653589793</v>
+        <v>316.346243104606</v>
       </c>
       <c r="M136" t="n">
         <v>7.92734376323774</v>
       </c>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="n">
-        <v>179.3146318707147</v>
+        <v>181.1452928466024</v>
       </c>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="b">
@@ -8715,14 +8715,14 @@
         <v>36</v>
       </c>
       <c r="L137" t="n">
-        <v>314.1592653589793</v>
+        <v>316.336112816567</v>
       </c>
       <c r="M137" t="n">
         <v>7.967648108362051</v>
       </c>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="n">
-        <v>175.6268913642302</v>
+        <v>178.7889751279239</v>
       </c>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="b">
@@ -8771,14 +8771,14 @@
         <v>37</v>
       </c>
       <c r="L138" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2260680509127</v>
       </c>
       <c r="M138" t="n">
         <v>8.467514839717863</v>
       </c>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="n">
-        <v>156.2610422305858</v>
+        <v>158.173188195218</v>
       </c>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="b">
@@ -8827,14 +8827,14 @@
         <v>38</v>
       </c>
       <c r="L139" t="n">
-        <v>314.1592653589793</v>
+        <v>316.248869489448</v>
       </c>
       <c r="M139" t="n">
         <v>8.625268164735836</v>
       </c>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="n">
-        <v>156.2610422305858</v>
+        <v>158.173188195218</v>
       </c>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="b">
@@ -8883,14 +8883,14 @@
         <v>39</v>
       </c>
       <c r="L140" t="n">
-        <v>314.1592653589793</v>
+        <v>316.240549678392</v>
       </c>
       <c r="M140" t="n">
         <v>8.731383266813546</v>
       </c>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="n">
-        <v>150.422316992052</v>
+        <v>152.1045352101532</v>
       </c>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="b">
@@ -8939,14 +8939,14 @@
         <v>40</v>
       </c>
       <c r="L141" t="n">
-        <v>314.1592653589793</v>
+        <v>318.0867669719897</v>
       </c>
       <c r="M141" t="n">
         <v>9.604645222832774</v>
       </c>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="n">
-        <v>122.9627839138132</v>
+        <v>123.891393669422</v>
       </c>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="b">
@@ -8995,14 +8995,14 @@
         <v>41</v>
       </c>
       <c r="L142" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3770358521283</v>
       </c>
       <c r="M142" t="n">
         <v>9.607600759090284</v>
       </c>
       <c r="N142" t="inlineStr"/>
       <c r="O142" t="n">
-        <v>122.9627839138132</v>
+        <v>123.891393669422</v>
       </c>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="b">
@@ -9051,13 +9051,13 @@
         <v>141</v>
       </c>
       <c r="L143" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6539549424615</v>
       </c>
       <c r="M143" t="n">
         <v>36.4287695490892</v>
       </c>
       <c r="N143" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
@@ -9107,13 +9107,13 @@
         <v>142</v>
       </c>
       <c r="L144" t="n">
-        <v>314.1592653589793</v>
+        <v>316.435102604766</v>
       </c>
       <c r="M144" t="n">
         <v>36.44705460040749</v>
       </c>
       <c r="N144" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
@@ -9163,13 +9163,13 @@
         <v>143</v>
       </c>
       <c r="L145" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3049316578601</v>
       </c>
       <c r="M145" t="n">
         <v>36.65623461726882</v>
       </c>
       <c r="N145" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="O145" t="inlineStr"/>
       <c r="P145" t="inlineStr"/>
@@ -9219,13 +9219,13 @@
         <v>144</v>
       </c>
       <c r="L146" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2687233454461</v>
       </c>
       <c r="M146" t="n">
         <v>36.78990436076752</v>
       </c>
       <c r="N146" t="n">
-        <v>135.9921309828678</v>
+        <v>162.3056812330665</v>
       </c>
       <c r="O146" t="inlineStr"/>
       <c r="P146" t="inlineStr"/>
@@ -9275,13 +9275,13 @@
         <v>145</v>
       </c>
       <c r="L147" t="n">
-        <v>314.1592653589793</v>
+        <v>316.2166706769734</v>
       </c>
       <c r="M147" t="n">
         <v>37.54182985071761</v>
       </c>
       <c r="N147" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="O147" t="inlineStr"/>
       <c r="P147" t="inlineStr"/>
@@ -9331,13 +9331,13 @@
         <v>146</v>
       </c>
       <c r="L148" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3449265579602</v>
       </c>
       <c r="M148" t="n">
         <v>37.98075074489766</v>
       </c>
       <c r="N148" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="O148" t="inlineStr"/>
       <c r="P148" t="inlineStr"/>
@@ -9387,13 +9387,13 @@
         <v>147</v>
       </c>
       <c r="L149" t="n">
-        <v>314.1592653589793</v>
+        <v>316.3255547191517</v>
       </c>
       <c r="M149" t="n">
         <v>38.03227681926045</v>
       </c>
       <c r="N149" t="n">
-        <v>175.9755522072987</v>
+        <v>177.7578780679024</v>
       </c>
       <c r="O149" t="inlineStr"/>
       <c r="P149" t="inlineStr"/>
@@ -9443,13 +9443,13 @@
         <v>148</v>
       </c>
       <c r="L150" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4511346509275</v>
       </c>
       <c r="M150" t="n">
         <v>38.49435885209373</v>
       </c>
       <c r="N150" t="n">
-        <v>195.3400059676167</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="O150" t="inlineStr"/>
       <c r="P150" t="inlineStr"/>
@@ -9499,13 +9499,13 @@
         <v>149</v>
       </c>
       <c r="L151" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5479574518906</v>
       </c>
       <c r="M151" t="n">
         <v>38.92118695951621</v>
       </c>
       <c r="N151" t="n">
-        <v>195.3400059676167</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="O151" t="inlineStr"/>
       <c r="P151" t="inlineStr"/>
@@ -9555,13 +9555,13 @@
         <v>150</v>
       </c>
       <c r="L152" t="n">
-        <v>314.1592653589793</v>
+        <v>316.7052154824808</v>
       </c>
       <c r="M152" t="n">
         <v>38.92529370923628</v>
       </c>
       <c r="N152" t="n">
-        <v>195.3400059676167</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="O152" t="inlineStr"/>
       <c r="P152" t="inlineStr"/>
@@ -9611,13 +9611,13 @@
         <v>151</v>
       </c>
       <c r="L153" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5485923506799</v>
       </c>
       <c r="M153" t="n">
         <v>38.93066753597672</v>
       </c>
       <c r="N153" t="n">
-        <v>195.3400059676167</v>
+        <v>201.5387278176926</v>
       </c>
       <c r="O153" t="inlineStr"/>
       <c r="P153" t="inlineStr"/>
@@ -9667,13 +9667,13 @@
         <v>152</v>
       </c>
       <c r="L154" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6194114183377</v>
       </c>
       <c r="M154" t="n">
         <v>39.47872534354801</v>
       </c>
       <c r="N154" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="O154" t="inlineStr"/>
       <c r="P154" t="inlineStr"/>
@@ -9723,13 +9723,13 @@
         <v>153</v>
       </c>
       <c r="L155" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6371955020049</v>
       </c>
       <c r="M155" t="n">
         <v>39.87996294801378</v>
       </c>
       <c r="N155" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="O155" t="inlineStr"/>
       <c r="P155" t="inlineStr"/>
@@ -9779,13 +9779,13 @@
         <v>154</v>
       </c>
       <c r="L156" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6496597587351</v>
       </c>
       <c r="M156" t="n">
         <v>39.90699501472117</v>
       </c>
       <c r="N156" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="O156" t="inlineStr"/>
       <c r="P156" t="inlineStr"/>
@@ -9835,13 +9835,13 @@
         <v>155</v>
       </c>
       <c r="L157" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6523253223867</v>
       </c>
       <c r="M157" t="n">
         <v>39.92225454572425</v>
       </c>
       <c r="N157" t="n">
-        <v>234.9184160202003</v>
+        <v>237.416804129758</v>
       </c>
       <c r="O157" t="inlineStr"/>
       <c r="P157" t="inlineStr"/>
@@ -9891,13 +9891,13 @@
         <v>156</v>
       </c>
       <c r="L158" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6216341209777</v>
       </c>
       <c r="M158" t="n">
         <v>40.45752601204321</v>
       </c>
       <c r="N158" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="O158" t="inlineStr"/>
       <c r="P158" t="inlineStr"/>
@@ -9947,13 +9947,13 @@
         <v>157</v>
       </c>
       <c r="L159" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6271737189013</v>
       </c>
       <c r="M159" t="n">
         <v>40.91891377405533</v>
       </c>
       <c r="N159" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="O159" t="inlineStr"/>
       <c r="P159" t="inlineStr"/>
@@ -10003,13 +10003,13 @@
         <v>158</v>
       </c>
       <c r="L160" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6030225734833</v>
       </c>
       <c r="M160" t="n">
         <v>40.93234294103283</v>
       </c>
       <c r="N160" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="O160" t="inlineStr"/>
       <c r="P160" t="inlineStr"/>
@@ -10059,13 +10059,13 @@
         <v>159</v>
       </c>
       <c r="L161" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6025425699355</v>
       </c>
       <c r="M161" t="n">
         <v>40.93935458082864</v>
       </c>
       <c r="N161" t="n">
-        <v>294.9855223413448</v>
+        <v>291.1335317844975</v>
       </c>
       <c r="O161" t="inlineStr"/>
       <c r="P161" t="inlineStr"/>
@@ -10115,13 +10115,13 @@
         <v>160</v>
       </c>
       <c r="L162" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5588351730509</v>
       </c>
       <c r="M162" t="n">
         <v>41.45353811274743</v>
       </c>
       <c r="N162" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="O162" t="inlineStr"/>
       <c r="P162" t="inlineStr"/>
@@ -10171,13 +10171,13 @@
         <v>161</v>
       </c>
       <c r="L163" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5324525438597</v>
       </c>
       <c r="M163" t="n">
         <v>41.94431431643077</v>
       </c>
       <c r="N163" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="O163" t="inlineStr"/>
       <c r="P163" t="inlineStr"/>
@@ -10227,13 +10227,13 @@
         <v>162</v>
       </c>
       <c r="L164" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6429017537891</v>
       </c>
       <c r="M164" t="n">
         <v>41.94818375850861</v>
       </c>
       <c r="N164" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="O164" t="inlineStr"/>
       <c r="P164" t="inlineStr"/>
@@ -10283,13 +10283,13 @@
         <v>163</v>
       </c>
       <c r="L165" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5472464894523</v>
       </c>
       <c r="M165" t="n">
         <v>41.9522351573759</v>
       </c>
       <c r="N165" t="n">
-        <v>295.365127176615</v>
+        <v>291.4729142988677</v>
       </c>
       <c r="O165" t="inlineStr"/>
       <c r="P165" t="inlineStr"/>
@@ -10339,13 +10339,13 @@
         <v>164</v>
       </c>
       <c r="L166" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5142305549545</v>
       </c>
       <c r="M166" t="n">
         <v>42.45531008200118</v>
       </c>
       <c r="N166" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="O166" t="inlineStr"/>
       <c r="P166" t="inlineStr"/>
@@ -10395,13 +10395,13 @@
         <v>165</v>
       </c>
       <c r="L167" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5033424213572</v>
       </c>
       <c r="M167" t="n">
         <v>42.95422684943781</v>
       </c>
       <c r="N167" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="O167" t="inlineStr"/>
       <c r="P167" t="inlineStr"/>
@@ -10451,13 +10451,13 @@
         <v>166</v>
       </c>
       <c r="L168" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5095522228258</v>
       </c>
       <c r="M168" t="n">
         <v>42.95892665090664</v>
       </c>
       <c r="N168" t="n">
-        <v>314.1592653589793</v>
+        <v>313.738845030075</v>
       </c>
       <c r="O168" t="inlineStr"/>
       <c r="P168" t="inlineStr"/>
@@ -10507,13 +10507,13 @@
         <v>167</v>
       </c>
       <c r="L169" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4977360874286</v>
       </c>
       <c r="M169" t="n">
         <v>43.45384558602582</v>
       </c>
       <c r="N169" t="n">
-        <v>314.1592653589793</v>
+        <v>316.1547027829528</v>
       </c>
       <c r="O169" t="inlineStr"/>
       <c r="P169" t="inlineStr"/>
@@ -10563,13 +10563,13 @@
         <v>168</v>
       </c>
       <c r="L170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5198963992781</v>
       </c>
       <c r="M170" t="n">
         <v>43.45616508508608</v>
       </c>
       <c r="N170" t="n">
-        <v>314.1592653589793</v>
+        <v>316.1547027829528</v>
       </c>
       <c r="O170" t="inlineStr"/>
       <c r="P170" t="inlineStr"/>
@@ -10619,13 +10619,13 @@
         <v>169</v>
       </c>
       <c r="L171" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949570043623</v>
       </c>
       <c r="M171" t="n">
         <v>43.95401374251702</v>
       </c>
       <c r="N171" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="O171" t="inlineStr"/>
       <c r="P171" t="inlineStr"/>
@@ -10675,13 +10675,13 @@
         <v>170</v>
       </c>
       <c r="L172" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4949217930474</v>
       </c>
       <c r="M172" t="n">
         <v>43.95617286453923</v>
       </c>
       <c r="N172" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
@@ -10731,13 +10731,13 @@
         <v>171</v>
       </c>
       <c r="L173" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938068880664</v>
       </c>
       <c r="M173" t="n">
         <v>44.4391289059291</v>
       </c>
       <c r="N173" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
@@ -10787,13 +10787,13 @@
         <v>172</v>
       </c>
       <c r="L174" t="n">
-        <v>314.1592653589793</v>
+        <v>324.3173917533691</v>
       </c>
       <c r="M174" t="n">
         <v>44.43916799494416</v>
       </c>
       <c r="N174" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
@@ -10843,13 +10843,13 @@
         <v>173</v>
       </c>
       <c r="L175" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5212865265892</v>
       </c>
       <c r="M175" t="n">
         <v>44.45925030955645</v>
       </c>
       <c r="N175" t="n">
-        <v>314.1592653589793</v>
+        <v>317.8526104247872</v>
       </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
@@ -10899,13 +10899,13 @@
         <v>174</v>
       </c>
       <c r="L176" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933431236824</v>
       </c>
       <c r="M176" t="n">
         <v>44.95030881886223</v>
       </c>
       <c r="N176" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6236624786501</v>
       </c>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
@@ -10955,13 +10955,13 @@
         <v>175</v>
       </c>
       <c r="L177" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4956969465613</v>
       </c>
       <c r="M177" t="n">
         <v>44.95224670009161</v>
       </c>
       <c r="N177" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6236624786501</v>
       </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
@@ -11011,13 +11011,13 @@
         <v>176</v>
       </c>
       <c r="L178" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4973241165592</v>
       </c>
       <c r="M178" t="n">
         <v>44.95495517007326</v>
       </c>
       <c r="N178" t="n">
-        <v>314.1592653589793</v>
+        <v>317.6236624786501</v>
       </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
@@ -11067,13 +11067,13 @@
         <v>177</v>
       </c>
       <c r="L179" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4931987137201</v>
       </c>
       <c r="M179" t="n">
         <v>45.43765181115788</v>
       </c>
       <c r="N179" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
@@ -11123,13 +11123,13 @@
         <v>178</v>
       </c>
       <c r="L180" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5195376879311</v>
       </c>
       <c r="M180" t="n">
         <v>45.43767532653112</v>
       </c>
       <c r="N180" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
@@ -11179,13 +11179,13 @@
         <v>179</v>
       </c>
       <c r="L181" t="n">
-        <v>314.1592653589793</v>
+        <v>316.5195338428691</v>
       </c>
       <c r="M181" t="n">
         <v>45.45778808805851</v>
       </c>
       <c r="N181" t="n">
-        <v>314.1592653589793</v>
+        <v>317.3627434845538</v>
       </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
@@ -11235,13 +11235,13 @@
         <v>180</v>
       </c>
       <c r="L182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4933080905907</v>
       </c>
       <c r="M182" t="n">
         <v>45.94675614107359</v>
       </c>
       <c r="N182" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6539549424615</v>
       </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
@@ -11291,13 +11291,13 @@
         <v>181</v>
       </c>
       <c r="L183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4938254204613</v>
       </c>
       <c r="M183" t="n">
         <v>45.94867875227989</v>
       </c>
       <c r="N183" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6539549424615</v>
       </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
@@ -11347,13 +11347,13 @@
         <v>182</v>
       </c>
       <c r="L184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.4951918035545</v>
       </c>
       <c r="M184" t="n">
         <v>45.95350055980311</v>
       </c>
       <c r="N184" t="n">
-        <v>314.1592653589793</v>
+        <v>316.6539549424615</v>
       </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
